--- a/outputs/tables/master_nsu_rename.xlsx
+++ b/outputs/tables/master_nsu_rename.xlsx
@@ -6884,19 +6884,28 @@
         <v>121</v>
       </c>
       <c r="D183" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E183" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F183" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G183" t="s">
-        <v>337</v>
+        <v>336</v>
+      </c>
+      <c r="H183" t="s">
+        <v>166</v>
       </c>
       <c r="I183" t="s">
-        <v>399</v>
+        <v>400</v>
+      </c>
+      <c r="J183" t="s">
+        <v>404</v>
+      </c>
+      <c r="K183" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -6910,29 +6919,23 @@
         <v>121</v>
       </c>
       <c r="D184" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E184" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="F184" t="s">
         <v>166</v>
       </c>
       <c r="G184" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H184" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I184" t="s">
         <v>400</v>
       </c>
-      <c r="J184" t="s">
-        <v>404</v>
-      </c>
-      <c r="K184" t="s">
-        <v>166</v>
-      </c>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
@@ -6945,22 +6948,19 @@
         <v>121</v>
       </c>
       <c r="D185" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E185" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F185" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="G185" t="s">
         <v>337</v>
       </c>
-      <c r="H185" t="s">
-        <v>141</v>
-      </c>
       <c r="I185" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -18837,19 +18837,22 @@
         <v>124</v>
       </c>
       <c r="D611" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E611" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F611" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G611" t="s">
         <v>337</v>
       </c>
+      <c r="H611" t="s">
+        <v>166</v>
+      </c>
       <c r="I611" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="612" spans="1:11">
@@ -18863,10 +18866,10 @@
         <v>124</v>
       </c>
       <c r="D612" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E612" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="F612" t="s">
         <v>166</v>
@@ -18875,7 +18878,7 @@
         <v>337</v>
       </c>
       <c r="H612" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I612" t="s">
         <v>400</v>
@@ -18892,22 +18895,19 @@
         <v>124</v>
       </c>
       <c r="D613" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E613" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F613" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="G613" t="s">
         <v>337</v>
       </c>
-      <c r="H613" t="s">
-        <v>141</v>
-      </c>
       <c r="I613" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="614" spans="1:11">

--- a/outputs/tables/master_nsu_rename.xlsx
+++ b/outputs/tables/master_nsu_rename.xlsx
@@ -1231,2830 +1231,2830 @@
     <t>nonsensical (recoverable)</t>
   </si>
   <si>
-    <t>11687.0</t>
-  </si>
-  <si>
-    <t>11779.0</t>
-  </si>
-  <si>
-    <t>11875.0</t>
-  </si>
-  <si>
-    <t>11496.0</t>
-  </si>
-  <si>
-    <t>11517.0</t>
-  </si>
-  <si>
-    <t>11537.0</t>
-  </si>
-  <si>
-    <t>11562.0</t>
-  </si>
-  <si>
-    <t>11575.0</t>
-  </si>
-  <si>
-    <t>11606.0</t>
-  </si>
-  <si>
-    <t>11611.0</t>
-  </si>
-  <si>
-    <t>11625.0</t>
-  </si>
-  <si>
-    <t>11639.0</t>
-  </si>
-  <si>
-    <t>11658.0</t>
-  </si>
-  <si>
-    <t>11672.0</t>
-  </si>
-  <si>
-    <t>11673.0</t>
-  </si>
-  <si>
-    <t>11671.0</t>
-  </si>
-  <si>
-    <t>11688.0</t>
-  </si>
-  <si>
-    <t>11706.0</t>
-  </si>
-  <si>
-    <t>11725.0</t>
-  </si>
-  <si>
-    <t>11742.0</t>
-  </si>
-  <si>
-    <t>11754.0</t>
-  </si>
-  <si>
-    <t>11789.0</t>
-  </si>
-  <si>
-    <t>11806.0</t>
-  </si>
-  <si>
-    <t>11819.0</t>
-  </si>
-  <si>
-    <t>11820.0</t>
-  </si>
-  <si>
-    <t>11888.0</t>
-  </si>
-  <si>
-    <t>11903.0</t>
-  </si>
-  <si>
-    <t>11911.0</t>
-  </si>
-  <si>
-    <t>11949.0</t>
-  </si>
-  <si>
-    <t>11984.0</t>
-  </si>
-  <si>
-    <t>11985.0</t>
-  </si>
-  <si>
-    <t>11994.0</t>
-  </si>
-  <si>
-    <t>12032.0</t>
-  </si>
-  <si>
-    <t>12051.0</t>
-  </si>
-  <si>
-    <t>12052.0</t>
-  </si>
-  <si>
-    <t>12053.0</t>
-  </si>
-  <si>
-    <t>12087.0</t>
-  </si>
-  <si>
-    <t>12112.0</t>
-  </si>
-  <si>
-    <t>12121.0</t>
-  </si>
-  <si>
-    <t>12122.0</t>
-  </si>
-  <si>
-    <t>12140.0</t>
-  </si>
-  <si>
-    <t>12152.0</t>
-  </si>
-  <si>
-    <t>12154.0</t>
-  </si>
-  <si>
-    <t>12153.0</t>
-  </si>
-  <si>
-    <t>12175.0</t>
-  </si>
-  <si>
-    <t>12179.0</t>
-  </si>
-  <si>
-    <t>12180.0</t>
-  </si>
-  <si>
-    <t>12193.0</t>
-  </si>
-  <si>
-    <t>12222.0</t>
-  </si>
-  <si>
-    <t>12232.0</t>
-  </si>
-  <si>
-    <t>12251.0</t>
-  </si>
-  <si>
-    <t>12263.0</t>
-  </si>
-  <si>
-    <t>12278.0</t>
-  </si>
-  <si>
-    <t>12277.0</t>
-  </si>
-  <si>
-    <t>12315.0</t>
-  </si>
-  <si>
-    <t>12333.0</t>
-  </si>
-  <si>
-    <t>12344.0</t>
-  </si>
-  <si>
-    <t>12356.0</t>
-  </si>
-  <si>
-    <t>12393.0</t>
-  </si>
-  <si>
-    <t>12398.0</t>
-  </si>
-  <si>
-    <t>11497.0</t>
-  </si>
-  <si>
-    <t>11641.0</t>
-  </si>
-  <si>
-    <t>11862.0</t>
-  </si>
-  <si>
-    <t>11951.0</t>
-  </si>
-  <si>
-    <t>11952.0</t>
-  </si>
-  <si>
-    <t>12142.0</t>
-  </si>
-  <si>
-    <t>12223.0</t>
-  </si>
-  <si>
-    <t>12295.0</t>
-  </si>
-  <si>
-    <t>12436.0</t>
-  </si>
-  <si>
-    <t>11518.0</t>
-  </si>
-  <si>
-    <t>11538.0</t>
-  </si>
-  <si>
-    <t>11563.0</t>
-  </si>
-  <si>
-    <t>11576.0</t>
-  </si>
-  <si>
-    <t>11597.0</t>
-  </si>
-  <si>
-    <t>11612.0</t>
-  </si>
-  <si>
-    <t>11626.0</t>
-  </si>
-  <si>
-    <t>11640.0</t>
-  </si>
-  <si>
-    <t>11674.0</t>
-  </si>
-  <si>
-    <t>11689.0</t>
-  </si>
-  <si>
-    <t>11707.0</t>
-  </si>
-  <si>
-    <t>11726.0</t>
-  </si>
-  <si>
-    <t>11743.0</t>
-  </si>
-  <si>
-    <t>11755.0</t>
-  </si>
-  <si>
-    <t>11780.0</t>
-  </si>
-  <si>
-    <t>11823.0</t>
-  </si>
-  <si>
-    <t>11831.0</t>
-  </si>
-  <si>
-    <t>11837.0</t>
-  </si>
-  <si>
-    <t>11852.0</t>
-  </si>
-  <si>
-    <t>11861.0</t>
-  </si>
-  <si>
-    <t>11876.0</t>
-  </si>
-  <si>
-    <t>11889.0</t>
-  </si>
-  <si>
-    <t>11936.0</t>
-  </si>
-  <si>
-    <t>11950.0</t>
-  </si>
-  <si>
-    <t>11970.0</t>
-  </si>
-  <si>
-    <t>12033.0</t>
-  </si>
-  <si>
-    <t>12054.0</t>
-  </si>
-  <si>
-    <t>12075.0</t>
-  </si>
-  <si>
-    <t>12113.0</t>
-  </si>
-  <si>
-    <t>12123.0</t>
-  </si>
-  <si>
-    <t>12141.0</t>
-  </si>
-  <si>
-    <t>12155.0</t>
-  </si>
-  <si>
-    <t>12233.0</t>
-  </si>
-  <si>
-    <t>12264.0</t>
-  </si>
-  <si>
-    <t>12294.0</t>
-  </si>
-  <si>
-    <t>12310.0</t>
-  </si>
-  <si>
-    <t>12316.0</t>
-  </si>
-  <si>
-    <t>12357.0</t>
-  </si>
-  <si>
-    <t>12371.0</t>
-  </si>
-  <si>
-    <t>12383.0</t>
-  </si>
-  <si>
-    <t>12399.0</t>
-  </si>
-  <si>
-    <t>12410.0</t>
-  </si>
-  <si>
-    <t>12420.0</t>
-  </si>
-  <si>
-    <t>12439.0</t>
-  </si>
-  <si>
-    <t>12442.0</t>
-  </si>
-  <si>
-    <t>12443.0</t>
-  </si>
-  <si>
-    <t>11498.0</t>
-  </si>
-  <si>
-    <t>11519.0</t>
-  </si>
-  <si>
-    <t>11539.0</t>
-  </si>
-  <si>
-    <t>11540.0</t>
-  </si>
-  <si>
-    <t>11549.0</t>
-  </si>
-  <si>
-    <t>11564.0</t>
-  </si>
-  <si>
-    <t>11577.0</t>
-  </si>
-  <si>
-    <t>11578.0</t>
-  </si>
-  <si>
-    <t>11607.0</t>
-  </si>
-  <si>
-    <t>11613.0</t>
-  </si>
-  <si>
-    <t>11627.0</t>
-  </si>
-  <si>
-    <t>11642.0</t>
-  </si>
-  <si>
-    <t>11659.0</t>
-  </si>
-  <si>
-    <t>11676.0</t>
-  </si>
-  <si>
-    <t>11675.0</t>
-  </si>
-  <si>
-    <t>11691.0</t>
-  </si>
-  <si>
-    <t>11690.0</t>
-  </si>
-  <si>
-    <t>11692.0</t>
-  </si>
-  <si>
-    <t>11708.0</t>
-  </si>
-  <si>
-    <t>11727.0</t>
-  </si>
-  <si>
-    <t>11744.0</t>
-  </si>
-  <si>
-    <t>11756.0</t>
-  </si>
-  <si>
-    <t>11757.0</t>
-  </si>
-  <si>
-    <t>11790.0</t>
-  </si>
-  <si>
-    <t>11807.0</t>
-  </si>
-  <si>
-    <t>11821.0</t>
-  </si>
-  <si>
-    <t>11832.0</t>
-  </si>
-  <si>
-    <t>11838.0</t>
-  </si>
-  <si>
-    <t>11863.0</t>
-  </si>
-  <si>
-    <t>11890.0</t>
-  </si>
-  <si>
-    <t>11891.0</t>
-  </si>
-  <si>
-    <t>11904.0</t>
-  </si>
-  <si>
-    <t>11912.0</t>
-  </si>
-  <si>
-    <t>11934.0</t>
-  </si>
-  <si>
-    <t>11937.0</t>
-  </si>
-  <si>
-    <t>11953.0</t>
-  </si>
-  <si>
-    <t>11995.0</t>
-  </si>
-  <si>
-    <t>12034.0</t>
-  </si>
-  <si>
-    <t>12055.0</t>
-  </si>
-  <si>
-    <t>12056.0</t>
-  </si>
-  <si>
-    <t>12088.0</t>
-  </si>
-  <si>
-    <t>12124.0</t>
-  </si>
-  <si>
-    <t>12125.0</t>
-  </si>
-  <si>
-    <t>12126.0</t>
-  </si>
-  <si>
-    <t>12143.0</t>
-  </si>
-  <si>
-    <t>12157.0</t>
-  </si>
-  <si>
-    <t>12156.0</t>
-  </si>
-  <si>
-    <t>12176.0</t>
-  </si>
-  <si>
-    <t>12181.0</t>
-  </si>
-  <si>
-    <t>12182.0</t>
-  </si>
-  <si>
-    <t>12183.0</t>
-  </si>
-  <si>
-    <t>12194.0</t>
-  </si>
-  <si>
-    <t>12225.0</t>
-  </si>
-  <si>
-    <t>12224.0</t>
-  </si>
-  <si>
-    <t>12252.0</t>
-  </si>
-  <si>
-    <t>12279.0</t>
-  </si>
-  <si>
-    <t>12311.0</t>
-  </si>
-  <si>
-    <t>12317.0</t>
-  </si>
-  <si>
-    <t>12334.0</t>
-  </si>
-  <si>
-    <t>12346.0</t>
-  </si>
-  <si>
-    <t>12345.0</t>
-  </si>
-  <si>
-    <t>12359.0</t>
-  </si>
-  <si>
-    <t>12358.0</t>
-  </si>
-  <si>
-    <t>12372.0</t>
-  </si>
-  <si>
-    <t>12394.0</t>
-  </si>
-  <si>
-    <t>12401.0</t>
-  </si>
-  <si>
-    <t>12400.0</t>
-  </si>
-  <si>
-    <t>11499.0</t>
-  </si>
-  <si>
-    <t>11550.0</t>
-  </si>
-  <si>
-    <t>11579.0</t>
-  </si>
-  <si>
-    <t>11601.0</t>
-  </si>
-  <si>
-    <t>11614.0</t>
-  </si>
-  <si>
-    <t>11615.0</t>
-  </si>
-  <si>
-    <t>11628.0</t>
-  </si>
-  <si>
-    <t>11643.0</t>
-  </si>
-  <si>
-    <t>11645.0</t>
-  </si>
-  <si>
-    <t>11644.0</t>
-  </si>
-  <si>
-    <t>11660.0</t>
-  </si>
-  <si>
-    <t>11662.0</t>
-  </si>
-  <si>
-    <t>11661.0</t>
-  </si>
-  <si>
-    <t>11677.0</t>
-  </si>
-  <si>
-    <t>11678.0</t>
-  </si>
-  <si>
-    <t>11693.0</t>
-  </si>
-  <si>
-    <t>11694.0</t>
-  </si>
-  <si>
-    <t>11709.0</t>
-  </si>
-  <si>
-    <t>11710.0</t>
-  </si>
-  <si>
-    <t>11728.0</t>
-  </si>
-  <si>
-    <t>11729.0</t>
-  </si>
-  <si>
-    <t>11745.0</t>
-  </si>
-  <si>
-    <t>11747.0</t>
-  </si>
-  <si>
-    <t>11746.0</t>
-  </si>
-  <si>
-    <t>11758.0</t>
-  </si>
-  <si>
-    <t>11759.0</t>
-  </si>
-  <si>
-    <t>11781.0</t>
-  </si>
-  <si>
-    <t>11782.0</t>
-  </si>
-  <si>
-    <t>11791.0</t>
-  </si>
-  <si>
-    <t>11792.0</t>
-  </si>
-  <si>
-    <t>11793.0</t>
-  </si>
-  <si>
-    <t>11808.0</t>
-  </si>
-  <si>
-    <t>11809.0</t>
-  </si>
-  <si>
-    <t>11824.0</t>
-  </si>
-  <si>
-    <t>11833.0</t>
-  </si>
-  <si>
-    <t>11834.0</t>
-  </si>
-  <si>
-    <t>11839.0</t>
-  </si>
-  <si>
-    <t>11853.0</t>
-  </si>
-  <si>
-    <t>11864.0</t>
-  </si>
-  <si>
-    <t>11865.0</t>
-  </si>
-  <si>
-    <t>11866.0</t>
-  </si>
-  <si>
-    <t>11867.0</t>
-  </si>
-  <si>
-    <t>11892.0</t>
-  </si>
-  <si>
-    <t>11905.0</t>
-  </si>
-  <si>
-    <t>11913.0</t>
-  </si>
-  <si>
-    <t>11930.0</t>
-  </si>
-  <si>
-    <t>11935.0</t>
-  </si>
-  <si>
-    <t>11954.0</t>
-  </si>
-  <si>
-    <t>11971.0</t>
-  </si>
-  <si>
-    <t>11986.0</t>
-  </si>
-  <si>
-    <t>11997.0</t>
-  </si>
-  <si>
-    <t>11996.0</t>
-  </si>
-  <si>
-    <t>11998.0</t>
-  </si>
-  <si>
-    <t>12007.0</t>
-  </si>
-  <si>
-    <t>12008.0</t>
-  </si>
-  <si>
-    <t>12021.0</t>
-  </si>
-  <si>
-    <t>12035.0</t>
-  </si>
-  <si>
-    <t>12057.0</t>
-  </si>
-  <si>
-    <t>12058.0</t>
-  </si>
-  <si>
-    <t>12059.0</t>
-  </si>
-  <si>
-    <t>12076.0</t>
-  </si>
-  <si>
-    <t>12083.0</t>
-  </si>
-  <si>
-    <t>12089.0</t>
-  </si>
-  <si>
-    <t>12095.0</t>
-  </si>
-  <si>
-    <t>12103.0</t>
-  </si>
-  <si>
-    <t>12114.0</t>
-  </si>
-  <si>
-    <t>12127.0</t>
-  </si>
-  <si>
-    <t>12144.0</t>
-  </si>
-  <si>
-    <t>12145.0</t>
-  </si>
-  <si>
-    <t>12158.0</t>
-  </si>
-  <si>
-    <t>12159.0</t>
-  </si>
-  <si>
-    <t>12160.0</t>
-  </si>
-  <si>
-    <t>12177.0</t>
-  </si>
-  <si>
-    <t>12184.0</t>
-  </si>
-  <si>
-    <t>12185.0</t>
-  </si>
-  <si>
-    <t>12195.0</t>
-  </si>
-  <si>
-    <t>12197.0</t>
-  </si>
-  <si>
-    <t>12196.0</t>
-  </si>
-  <si>
-    <t>12208.0</t>
-  </si>
-  <si>
-    <t>12210.0</t>
-  </si>
-  <si>
-    <t>12209.0</t>
-  </si>
-  <si>
-    <t>12226.0</t>
-  </si>
-  <si>
-    <t>12234.0</t>
-  </si>
-  <si>
-    <t>12253.0</t>
-  </si>
-  <si>
-    <t>12254.0</t>
-  </si>
-  <si>
-    <t>12265.0</t>
-  </si>
-  <si>
-    <t>12280.0</t>
-  </si>
-  <si>
-    <t>12282.0</t>
-  </si>
-  <si>
-    <t>12281.0</t>
-  </si>
-  <si>
-    <t>12296.0</t>
-  </si>
-  <si>
-    <t>12297.0</t>
-  </si>
-  <si>
-    <t>12312.0</t>
-  </si>
-  <si>
-    <t>12318.0</t>
-  </si>
-  <si>
-    <t>12328.0</t>
-  </si>
-  <si>
-    <t>12335.0</t>
-  </si>
-  <si>
-    <t>12347.0</t>
-  </si>
-  <si>
-    <t>12360.0</t>
-  </si>
-  <si>
-    <t>12361.0</t>
-  </si>
-  <si>
-    <t>12370.0</t>
-  </si>
-  <si>
-    <t>12381.0</t>
-  </si>
-  <si>
-    <t>12384.0</t>
-  </si>
-  <si>
-    <t>12403.0</t>
-  </si>
-  <si>
-    <t>12402.0</t>
-  </si>
-  <si>
-    <t>12404.0</t>
-  </si>
-  <si>
-    <t>12411.0</t>
-  </si>
-  <si>
-    <t>12412.0</t>
-  </si>
-  <si>
-    <t>12421.0</t>
-  </si>
-  <si>
-    <t>12426.0</t>
-  </si>
-  <si>
-    <t>12429.0</t>
-  </si>
-  <si>
-    <t>12431.0</t>
-  </si>
-  <si>
-    <t>12435.0</t>
-  </si>
-  <si>
-    <t>12438.0</t>
-  </si>
-  <si>
-    <t>12440.0</t>
-  </si>
-  <si>
-    <t>12441.0</t>
-  </si>
-  <si>
-    <t>11520.0</t>
-  </si>
-  <si>
-    <t>11528.0</t>
-  </si>
-  <si>
-    <t>11529.0</t>
-  </si>
-  <si>
-    <t>11530.0</t>
-  </si>
-  <si>
-    <t>11565.0</t>
-  </si>
-  <si>
-    <t>11590.0</t>
-  </si>
-  <si>
-    <t>11589.0</t>
-  </si>
-  <si>
-    <t>11629.0</t>
-  </si>
-  <si>
-    <t>11646.0</t>
-  </si>
-  <si>
-    <t>11647.0</t>
-  </si>
-  <si>
-    <t>11663.0</t>
-  </si>
-  <si>
-    <t>11679.0</t>
-  </si>
-  <si>
-    <t>11794.0</t>
-  </si>
-  <si>
-    <t>11840.0</t>
-  </si>
-  <si>
-    <t>11841.0</t>
-  </si>
-  <si>
-    <t>11842.0</t>
-  </si>
-  <si>
-    <t>11938.0</t>
-  </si>
-  <si>
-    <t>11987.0</t>
-  </si>
-  <si>
-    <t>11999.0</t>
-  </si>
-  <si>
-    <t>12009.0</t>
-  </si>
-  <si>
-    <t>12022.0</t>
-  </si>
-  <si>
-    <t>12060.0</t>
-  </si>
-  <si>
-    <t>12077.0</t>
-  </si>
-  <si>
-    <t>12090.0</t>
-  </si>
-  <si>
-    <t>12115.0</t>
-  </si>
-  <si>
-    <t>12128.0</t>
-  </si>
-  <si>
-    <t>12146.0</t>
-  </si>
-  <si>
-    <t>12198.0</t>
-  </si>
-  <si>
-    <t>12236.0</t>
-  </si>
-  <si>
-    <t>12235.0</t>
-  </si>
-  <si>
-    <t>12266.0</t>
-  </si>
-  <si>
-    <t>12283.0</t>
-  </si>
-  <si>
-    <t>12298.0</t>
-  </si>
-  <si>
-    <t>12319.0</t>
-  </si>
-  <si>
-    <t>12395.0</t>
-  </si>
-  <si>
-    <t>11500.0</t>
-  </si>
-  <si>
-    <t>11580.0</t>
-  </si>
-  <si>
-    <t>11591.0</t>
-  </si>
-  <si>
-    <t>11602.0</t>
-  </si>
-  <si>
-    <t>11877.0</t>
-  </si>
-  <si>
-    <t>11931.0</t>
-  </si>
-  <si>
-    <t>11955.0</t>
-  </si>
-  <si>
-    <t>11972.0</t>
-  </si>
-  <si>
-    <t>12010.0</t>
-  </si>
-  <si>
-    <t>12147.0</t>
-  </si>
-  <si>
-    <t>12267.0</t>
-  </si>
-  <si>
-    <t>12437.0</t>
-  </si>
-  <si>
-    <t>11680.0</t>
-  </si>
-  <si>
-    <t>11711.0</t>
-  </si>
-  <si>
-    <t>11712.0</t>
-  </si>
-  <si>
-    <t>11825.0</t>
-  </si>
-  <si>
-    <t>11854.0</t>
-  </si>
-  <si>
-    <t>11868.0</t>
-  </si>
-  <si>
-    <t>11914.0</t>
-  </si>
-  <si>
-    <t>11916.0</t>
-  </si>
-  <si>
-    <t>11915.0</t>
-  </si>
-  <si>
-    <t>11956.0</t>
-  </si>
-  <si>
-    <t>11957.0</t>
-  </si>
-  <si>
-    <t>11988.0</t>
-  </si>
-  <si>
-    <t>12011.0</t>
-  </si>
-  <si>
-    <t>12023.0</t>
-  </si>
-  <si>
-    <t>12061.0</t>
-  </si>
-  <si>
-    <t>12062.0</t>
-  </si>
-  <si>
-    <t>12063.0</t>
-  </si>
-  <si>
-    <t>12064.0</t>
-  </si>
-  <si>
-    <t>12129.0</t>
-  </si>
-  <si>
-    <t>12130.0</t>
-  </si>
-  <si>
-    <t>12131.0</t>
-  </si>
-  <si>
-    <t>12148.0</t>
-  </si>
-  <si>
-    <t>12149.0</t>
-  </si>
-  <si>
-    <t>12162.0</t>
-  </si>
-  <si>
-    <t>12161.0</t>
-  </si>
-  <si>
-    <t>12163.0</t>
-  </si>
-  <si>
-    <t>12171.0</t>
-  </si>
-  <si>
-    <t>12172.0</t>
-  </si>
-  <si>
-    <t>12173.0</t>
-  </si>
-  <si>
-    <t>12200.0</t>
-  </si>
-  <si>
-    <t>12199.0</t>
-  </si>
-  <si>
-    <t>12237.0</t>
-  </si>
-  <si>
-    <t>12238.0</t>
-  </si>
-  <si>
-    <t>12284.0</t>
-  </si>
-  <si>
-    <t>12300.0</t>
-  </si>
-  <si>
-    <t>12299.0</t>
-  </si>
-  <si>
-    <t>12348.0</t>
-  </si>
-  <si>
-    <t>12373.0</t>
-  </si>
-  <si>
-    <t>12374.0</t>
-  </si>
-  <si>
-    <t>12375.0</t>
-  </si>
-  <si>
-    <t>12386.0</t>
-  </si>
-  <si>
-    <t>12385.0</t>
-  </si>
-  <si>
-    <t>12405.0</t>
-  </si>
-  <si>
-    <t>12413.0</t>
-  </si>
-  <si>
-    <t>12422.0</t>
-  </si>
-  <si>
-    <t>11502.0</t>
-  </si>
-  <si>
-    <t>11505.0</t>
-  </si>
-  <si>
-    <t>11503.0</t>
-  </si>
-  <si>
-    <t>11504.0</t>
-  </si>
-  <si>
-    <t>11515.0</t>
-  </si>
-  <si>
-    <t>11521.0</t>
-  </si>
-  <si>
-    <t>11522.0</t>
-  </si>
-  <si>
-    <t>11531.0</t>
-  </si>
-  <si>
-    <t>11541.0</t>
-  </si>
-  <si>
-    <t>11543.0</t>
-  </si>
-  <si>
-    <t>11542.0</t>
-  </si>
-  <si>
-    <t>11551.0</t>
-  </si>
-  <si>
-    <t>11552.0</t>
-  </si>
-  <si>
-    <t>11567.0</t>
-  </si>
-  <si>
-    <t>11568.0</t>
-  </si>
-  <si>
-    <t>11566.0</t>
-  </si>
-  <si>
-    <t>11581.0</t>
-  </si>
-  <si>
-    <t>11582.0</t>
-  </si>
-  <si>
-    <t>11598.0</t>
-  </si>
-  <si>
-    <t>11603.0</t>
-  </si>
-  <si>
-    <t>11616.0</t>
-  </si>
-  <si>
-    <t>11617.0</t>
-  </si>
-  <si>
-    <t>11630.0</t>
-  </si>
-  <si>
-    <t>11648.0</t>
-  </si>
-  <si>
-    <t>11649.0</t>
-  </si>
-  <si>
-    <t>11664.0</t>
-  </si>
-  <si>
-    <t>11665.0</t>
-  </si>
-  <si>
-    <t>11681.0</t>
-  </si>
-  <si>
-    <t>11695.0</t>
-  </si>
-  <si>
-    <t>11696.0</t>
-  </si>
-  <si>
-    <t>11713.0</t>
-  </si>
-  <si>
-    <t>11714.0</t>
-  </si>
-  <si>
-    <t>11715.0</t>
-  </si>
-  <si>
-    <t>11716.0</t>
-  </si>
-  <si>
-    <t>11730.0</t>
-  </si>
-  <si>
-    <t>11731.0</t>
-  </si>
-  <si>
-    <t>11732.0</t>
-  </si>
-  <si>
-    <t>11748.0</t>
-  </si>
-  <si>
-    <t>11749.0</t>
-  </si>
-  <si>
-    <t>11760.0</t>
-  </si>
-  <si>
-    <t>11761.0</t>
-  </si>
-  <si>
-    <t>11762.0</t>
-  </si>
-  <si>
-    <t>11763.0</t>
-  </si>
-  <si>
-    <t>11764.0</t>
-  </si>
-  <si>
-    <t>11783.0</t>
-  </si>
-  <si>
-    <t>11795.0</t>
-  </si>
-  <si>
-    <t>11796.0</t>
-  </si>
-  <si>
-    <t>11797.0</t>
-  </si>
-  <si>
-    <t>11798.0</t>
-  </si>
-  <si>
-    <t>11810.0</t>
-  </si>
-  <si>
-    <t>11811.0</t>
-  </si>
-  <si>
-    <t>11816.0</t>
-  </si>
-  <si>
-    <t>11826.0</t>
-  </si>
-  <si>
-    <t>11843.0</t>
-  </si>
-  <si>
-    <t>11844.0</t>
-  </si>
-  <si>
-    <t>11855.0</t>
-  </si>
-  <si>
-    <t>11869.0</t>
-  </si>
-  <si>
-    <t>11879.0</t>
-  </si>
-  <si>
-    <t>11878.0</t>
-  </si>
-  <si>
-    <t>11881.0</t>
-  </si>
-  <si>
-    <t>11880.0</t>
-  </si>
-  <si>
-    <t>11893.0</t>
-  </si>
-  <si>
-    <t>11906.0</t>
-  </si>
-  <si>
-    <t>11917.0</t>
-  </si>
-  <si>
-    <t>11918.0</t>
-  </si>
-  <si>
-    <t>11920.0</t>
-  </si>
-  <si>
-    <t>11921.0</t>
-  </si>
-  <si>
-    <t>11919.0</t>
-  </si>
-  <si>
-    <t>11932.0</t>
-  </si>
-  <si>
-    <t>11939.0</t>
-  </si>
-  <si>
-    <t>11940.0</t>
-  </si>
-  <si>
-    <t>11958.0</t>
-  </si>
-  <si>
-    <t>11960.0</t>
-  </si>
-  <si>
-    <t>11974.0</t>
-  </si>
-  <si>
-    <t>11973.0</t>
-  </si>
-  <si>
-    <t>11989.0</t>
-  </si>
-  <si>
-    <t>12000.0</t>
-  </si>
-  <si>
-    <t>12001.0</t>
-  </si>
-  <si>
-    <t>12024.0</t>
-  </si>
-  <si>
-    <t>12036.0</t>
-  </si>
-  <si>
-    <t>12037.0</t>
-  </si>
-  <si>
-    <t>12066.0</t>
-  </si>
-  <si>
-    <t>12065.0</t>
-  </si>
-  <si>
-    <t>12078.0</t>
-  </si>
-  <si>
-    <t>12096.0</t>
-  </si>
-  <si>
-    <t>12104.0</t>
-  </si>
-  <si>
-    <t>12132.0</t>
-  </si>
-  <si>
-    <t>12164.0</t>
-  </si>
-  <si>
-    <t>12201.0</t>
-  </si>
-  <si>
-    <t>12202.0</t>
-  </si>
-  <si>
-    <t>12211.0</t>
-  </si>
-  <si>
-    <t>12212.0</t>
-  </si>
-  <si>
-    <t>12213.0</t>
-  </si>
-  <si>
-    <t>12227.0</t>
-  </si>
-  <si>
-    <t>12239.0</t>
-  </si>
-  <si>
-    <t>12240.0</t>
-  </si>
-  <si>
-    <t>12241.0</t>
-  </si>
-  <si>
-    <t>12257.0</t>
-  </si>
-  <si>
-    <t>12255.0</t>
-  </si>
-  <si>
-    <t>12256.0</t>
-  </si>
-  <si>
-    <t>12268.0</t>
-  </si>
-  <si>
-    <t>12285.0</t>
-  </si>
-  <si>
-    <t>12286.0</t>
-  </si>
-  <si>
-    <t>12287.0</t>
-  </si>
-  <si>
-    <t>12301.0</t>
-  </si>
-  <si>
-    <t>12313.0</t>
-  </si>
-  <si>
-    <t>12321.0</t>
-  </si>
-  <si>
-    <t>12336.0</t>
-  </si>
-  <si>
-    <t>12349.0</t>
-  </si>
-  <si>
-    <t>12362.0</t>
-  </si>
-  <si>
-    <t>12363.0</t>
-  </si>
-  <si>
-    <t>12387.0</t>
-  </si>
-  <si>
-    <t>12419.0</t>
-  </si>
-  <si>
-    <t>12428.0</t>
-  </si>
-  <si>
-    <t>12427.0</t>
-  </si>
-  <si>
-    <t>12432.0</t>
-  </si>
-  <si>
-    <t>11506.0</t>
-  </si>
-  <si>
-    <t>11523.0</t>
-  </si>
-  <si>
-    <t>11532.0</t>
-  </si>
-  <si>
-    <t>11544.0</t>
-  </si>
-  <si>
-    <t>11553.0</t>
-  </si>
-  <si>
-    <t>11569.0</t>
-  </si>
-  <si>
-    <t>11583.0</t>
-  </si>
-  <si>
-    <t>11608.0</t>
-  </si>
-  <si>
-    <t>11609.0</t>
-  </si>
-  <si>
-    <t>11733.0</t>
-  </si>
-  <si>
-    <t>11734.0</t>
-  </si>
-  <si>
-    <t>11765.0</t>
-  </si>
-  <si>
-    <t>11766.0</t>
-  </si>
-  <si>
-    <t>11767.0</t>
-  </si>
-  <si>
-    <t>11768.0</t>
-  </si>
-  <si>
-    <t>11769.0</t>
-  </si>
-  <si>
-    <t>11799.0</t>
-  </si>
-  <si>
-    <t>11922.0</t>
-  </si>
-  <si>
-    <t>11941.0</t>
-  </si>
-  <si>
-    <t>11961.0</t>
-  </si>
-  <si>
-    <t>11975.0</t>
-  </si>
-  <si>
-    <t>12002.0</t>
-  </si>
-  <si>
-    <t>12178.0</t>
-  </si>
-  <si>
-    <t>12187.0</t>
-  </si>
-  <si>
-    <t>12188.0</t>
-  </si>
-  <si>
-    <t>12214.0</t>
-  </si>
-  <si>
-    <t>12414.0</t>
-  </si>
-  <si>
-    <t>11508.0</t>
-  </si>
-  <si>
-    <t>11509.0</t>
-  </si>
-  <si>
-    <t>11507.0</t>
-  </si>
-  <si>
-    <t>11524.0</t>
-  </si>
-  <si>
-    <t>11533.0</t>
-  </si>
-  <si>
-    <t>11534.0</t>
-  </si>
-  <si>
-    <t>11545.0</t>
-  </si>
-  <si>
-    <t>11547.0</t>
-  </si>
-  <si>
-    <t>11546.0</t>
-  </si>
-  <si>
-    <t>11555.0</t>
-  </si>
-  <si>
-    <t>11554.0</t>
-  </si>
-  <si>
-    <t>11557.0</t>
-  </si>
-  <si>
-    <t>11556.0</t>
-  </si>
-  <si>
-    <t>11558.0</t>
-  </si>
-  <si>
-    <t>11571.0</t>
-  </si>
-  <si>
-    <t>11570.0</t>
-  </si>
-  <si>
-    <t>11572.0</t>
-  </si>
-  <si>
-    <t>11585.0</t>
-  </si>
-  <si>
-    <t>11584.0</t>
-  </si>
-  <si>
-    <t>11586.0</t>
-  </si>
-  <si>
-    <t>11592.0</t>
-  </si>
-  <si>
-    <t>11593.0</t>
-  </si>
-  <si>
-    <t>11599.0</t>
-  </si>
-  <si>
-    <t>11610.0</t>
-  </si>
-  <si>
-    <t>11618.0</t>
-  </si>
-  <si>
-    <t>11620.0</t>
-  </si>
-  <si>
-    <t>11619.0</t>
-  </si>
-  <si>
-    <t>11621.0</t>
-  </si>
-  <si>
-    <t>11631.0</t>
-  </si>
-  <si>
-    <t>11632.0</t>
-  </si>
-  <si>
-    <t>11634.0</t>
-  </si>
-  <si>
-    <t>11633.0</t>
-  </si>
-  <si>
-    <t>11635.0</t>
-  </si>
-  <si>
-    <t>11650.0</t>
-  </si>
-  <si>
-    <t>11651.0</t>
-  </si>
-  <si>
-    <t>11652.0</t>
-  </si>
-  <si>
-    <t>11653.0</t>
-  </si>
-  <si>
-    <t>11666.0</t>
-  </si>
-  <si>
-    <t>11682.0</t>
-  </si>
-  <si>
-    <t>11683.0</t>
-  </si>
-  <si>
-    <t>11684.0</t>
-  </si>
-  <si>
-    <t>11697.0</t>
-  </si>
-  <si>
-    <t>11698.0</t>
-  </si>
-  <si>
-    <t>11699.0</t>
-  </si>
-  <si>
-    <t>11700.0</t>
-  </si>
-  <si>
-    <t>11701.0</t>
-  </si>
-  <si>
-    <t>11717.0</t>
-  </si>
-  <si>
-    <t>11719.0</t>
-  </si>
-  <si>
-    <t>11718.0</t>
-  </si>
-  <si>
-    <t>11720.0</t>
-  </si>
-  <si>
-    <t>11735.0</t>
-  </si>
-  <si>
-    <t>11736.0</t>
-  </si>
-  <si>
-    <t>11737.0</t>
-  </si>
-  <si>
-    <t>11738.0</t>
-  </si>
-  <si>
-    <t>11750.0</t>
-  </si>
-  <si>
-    <t>11751.0</t>
-  </si>
-  <si>
-    <t>11771.0</t>
-  </si>
-  <si>
-    <t>11772.0</t>
-  </si>
-  <si>
-    <t>11770.0</t>
-  </si>
-  <si>
-    <t>11773.0</t>
-  </si>
-  <si>
-    <t>11784.0</t>
-  </si>
-  <si>
-    <t>11785.0</t>
-  </si>
-  <si>
-    <t>11800.0</t>
-  </si>
-  <si>
-    <t>11801.0</t>
-  </si>
-  <si>
-    <t>11817.0</t>
-  </si>
-  <si>
-    <t>11827.0</t>
-  </si>
-  <si>
-    <t>11828.0</t>
-  </si>
-  <si>
-    <t>11829.0</t>
-  </si>
-  <si>
-    <t>11845.0</t>
-  </si>
-  <si>
-    <t>11847.0</t>
-  </si>
-  <si>
-    <t>11846.0</t>
-  </si>
-  <si>
-    <t>11848.0</t>
-  </si>
-  <si>
-    <t>11849.0</t>
-  </si>
-  <si>
-    <t>11857.0</t>
-  </si>
-  <si>
-    <t>11856.0</t>
-  </si>
-  <si>
-    <t>11858.0</t>
-  </si>
-  <si>
-    <t>11870.0</t>
-  </si>
-  <si>
-    <t>11871.0</t>
-  </si>
-  <si>
-    <t>11872.0</t>
-  </si>
-  <si>
-    <t>11883.0</t>
-  </si>
-  <si>
-    <t>11884.0</t>
-  </si>
-  <si>
-    <t>11882.0</t>
-  </si>
-  <si>
-    <t>11885.0</t>
-  </si>
-  <si>
-    <t>11894.0</t>
-  </si>
-  <si>
-    <t>11896.0</t>
-  </si>
-  <si>
-    <t>11897.0</t>
-  </si>
-  <si>
-    <t>11898.0</t>
-  </si>
-  <si>
-    <t>11895.0</t>
-  </si>
-  <si>
-    <t>11899.0</t>
-  </si>
-  <si>
-    <t>11907.0</t>
-  </si>
-  <si>
-    <t>11908.0</t>
-  </si>
-  <si>
-    <t>11909.0</t>
-  </si>
-  <si>
-    <t>11910.0</t>
-  </si>
-  <si>
-    <t>11924.0</t>
-  </si>
-  <si>
-    <t>11925.0</t>
-  </si>
-  <si>
-    <t>11926.0</t>
-  </si>
-  <si>
-    <t>11923.0</t>
-  </si>
-  <si>
-    <t>11927.0</t>
-  </si>
-  <si>
-    <t>11928.0</t>
-  </si>
-  <si>
-    <t>11942.0</t>
-  </si>
-  <si>
-    <t>11943.0</t>
-  </si>
-  <si>
-    <t>11944.0</t>
-  </si>
-  <si>
-    <t>11945.0</t>
-  </si>
-  <si>
-    <t>11963.0</t>
-  </si>
-  <si>
-    <t>11964.0</t>
-  </si>
-  <si>
-    <t>11962.0</t>
-  </si>
-  <si>
-    <t>11965.0</t>
-  </si>
-  <si>
-    <t>11966.0</t>
-  </si>
-  <si>
-    <t>11977.0</t>
-  </si>
-  <si>
-    <t>11978.0</t>
-  </si>
-  <si>
-    <t>11976.0</t>
-  </si>
-  <si>
-    <t>11979.0</t>
-  </si>
-  <si>
-    <t>11980.0</t>
-  </si>
-  <si>
-    <t>11990.0</t>
-  </si>
-  <si>
-    <t>11991.0</t>
-  </si>
-  <si>
-    <t>12003.0</t>
-  </si>
-  <si>
-    <t>12004.0</t>
-  </si>
-  <si>
-    <t>12005.0</t>
-  </si>
-  <si>
-    <t>12006.0</t>
-  </si>
-  <si>
-    <t>12012.0</t>
-  </si>
-  <si>
-    <t>12014.0</t>
-  </si>
-  <si>
-    <t>12013.0</t>
-  </si>
-  <si>
-    <t>12015.0</t>
-  </si>
-  <si>
-    <t>12016.0</t>
-  </si>
-  <si>
-    <t>12025.0</t>
-  </si>
-  <si>
-    <t>12027.0</t>
-  </si>
-  <si>
-    <t>12026.0</t>
-  </si>
-  <si>
-    <t>12028.0</t>
-  </si>
-  <si>
-    <t>12038.0</t>
-  </si>
-  <si>
-    <t>12040.0</t>
-  </si>
-  <si>
-    <t>12041.0</t>
-  </si>
-  <si>
-    <t>12039.0</t>
-  </si>
-  <si>
-    <t>12042.0</t>
-  </si>
-  <si>
-    <t>12043.0</t>
-  </si>
-  <si>
-    <t>12047.0</t>
-  </si>
-  <si>
-    <t>12048.0</t>
-  </si>
-  <si>
-    <t>12067.0</t>
-  </si>
-  <si>
-    <t>12068.0</t>
-  </si>
-  <si>
-    <t>12069.0</t>
-  </si>
-  <si>
-    <t>12070.0</t>
-  </si>
-  <si>
-    <t>12079.0</t>
-  </si>
-  <si>
-    <t>12080.0</t>
-  </si>
-  <si>
-    <t>12081.0</t>
-  </si>
-  <si>
-    <t>12084.0</t>
-  </si>
-  <si>
-    <t>12085.0</t>
-  </si>
-  <si>
-    <t>12091.0</t>
-  </si>
-  <si>
-    <t>12097.0</t>
-  </si>
-  <si>
-    <t>12098.0</t>
-  </si>
-  <si>
-    <t>12099.0</t>
-  </si>
-  <si>
-    <t>12105.0</t>
-  </si>
-  <si>
-    <t>12106.0</t>
-  </si>
-  <si>
-    <t>12107.0</t>
-  </si>
-  <si>
-    <t>12116.0</t>
-  </si>
-  <si>
-    <t>12117.0</t>
-  </si>
-  <si>
-    <t>12118.0</t>
-  </si>
-  <si>
-    <t>12134.0</t>
-  </si>
-  <si>
-    <t>12135.0</t>
-  </si>
-  <si>
-    <t>12133.0</t>
-  </si>
-  <si>
-    <t>12136.0</t>
-  </si>
-  <si>
-    <t>12189.0</t>
-  </si>
-  <si>
-    <t>12190.0</t>
-  </si>
-  <si>
-    <t>12191.0</t>
-  </si>
-  <si>
-    <t>12203.0</t>
-  </si>
-  <si>
-    <t>12205.0</t>
-  </si>
-  <si>
-    <t>12204.0</t>
-  </si>
-  <si>
-    <t>12206.0</t>
-  </si>
-  <si>
-    <t>12215.0</t>
-  </si>
-  <si>
-    <t>12216.0</t>
-  </si>
-  <si>
-    <t>12218.0</t>
-  </si>
-  <si>
-    <t>12217.0</t>
-  </si>
-  <si>
-    <t>12219.0</t>
-  </si>
-  <si>
-    <t>12229.0</t>
-  </si>
-  <si>
-    <t>12228.0</t>
-  </si>
-  <si>
-    <t>12230.0</t>
-  </si>
-  <si>
-    <t>12242.0</t>
-  </si>
-  <si>
-    <t>12244.0</t>
-  </si>
-  <si>
-    <t>12245.0</t>
-  </si>
-  <si>
-    <t>12243.0</t>
-  </si>
-  <si>
-    <t>12246.0</t>
-  </si>
-  <si>
-    <t>12247.0</t>
-  </si>
-  <si>
-    <t>12258.0</t>
-  </si>
-  <si>
-    <t>12260.0</t>
-  </si>
-  <si>
-    <t>12259.0</t>
-  </si>
-  <si>
-    <t>12269.0</t>
-  </si>
-  <si>
-    <t>12271.0</t>
-  </si>
-  <si>
-    <t>12270.0</t>
-  </si>
-  <si>
-    <t>12272.0</t>
-  </si>
-  <si>
-    <t>12273.0</t>
-  </si>
-  <si>
-    <t>12289.0</t>
-  </si>
-  <si>
-    <t>12288.0</t>
-  </si>
-  <si>
-    <t>12290.0</t>
-  </si>
-  <si>
-    <t>12302.0</t>
-  </si>
-  <si>
-    <t>12304.0</t>
-  </si>
-  <si>
-    <t>12303.0</t>
-  </si>
-  <si>
-    <t>12305.0</t>
-  </si>
-  <si>
-    <t>12323.0</t>
-  </si>
-  <si>
-    <t>12322.0</t>
-  </si>
-  <si>
-    <t>12324.0</t>
-  </si>
-  <si>
-    <t>12329.0</t>
-  </si>
-  <si>
-    <t>12330.0</t>
-  </si>
-  <si>
-    <t>12331.0</t>
-  </si>
-  <si>
-    <t>12337.0</t>
-  </si>
-  <si>
-    <t>12339.0</t>
-  </si>
-  <si>
-    <t>12338.0</t>
-  </si>
-  <si>
-    <t>12340.0</t>
-  </si>
-  <si>
-    <t>12350.0</t>
-  </si>
-  <si>
-    <t>12351.0</t>
-  </si>
-  <si>
-    <t>12352.0</t>
-  </si>
-  <si>
-    <t>12364.0</t>
-  </si>
-  <si>
-    <t>12365.0</t>
-  </si>
-  <si>
-    <t>12366.0</t>
-  </si>
-  <si>
-    <t>12367.0</t>
-  </si>
-  <si>
-    <t>12368.0</t>
-  </si>
-  <si>
-    <t>12376.0</t>
-  </si>
-  <si>
-    <t>12377.0</t>
-  </si>
-  <si>
-    <t>12388.0</t>
-  </si>
-  <si>
-    <t>12389.0</t>
-  </si>
-  <si>
-    <t>12390.0</t>
-  </si>
-  <si>
-    <t>12396.0</t>
-  </si>
-  <si>
-    <t>12397.0</t>
-  </si>
-  <si>
-    <t>12406.0</t>
-  </si>
-  <si>
-    <t>12407.0</t>
-  </si>
-  <si>
-    <t>12408.0</t>
-  </si>
-  <si>
-    <t>12415.0</t>
-  </si>
-  <si>
-    <t>12416.0</t>
-  </si>
-  <si>
-    <t>12444.0</t>
-  </si>
-  <si>
-    <t>11510.0</t>
-  </si>
-  <si>
-    <t>11774.0</t>
-  </si>
-  <si>
-    <t>11859.0</t>
-  </si>
-  <si>
-    <t>11886.0</t>
-  </si>
-  <si>
-    <t>12017.0</t>
-  </si>
-  <si>
-    <t>12409.0</t>
-  </si>
-  <si>
-    <t>12433.0</t>
-  </si>
-  <si>
-    <t>11654.0</t>
-  </si>
-  <si>
-    <t>11981.0</t>
-  </si>
-  <si>
-    <t>12100.0</t>
-  </si>
-  <si>
-    <t>11702.0</t>
-  </si>
-  <si>
-    <t>11900.0</t>
-  </si>
-  <si>
-    <t>12092.0</t>
-  </si>
-  <si>
-    <t>12306.0</t>
-  </si>
-  <si>
-    <t>12332.0</t>
-  </si>
-  <si>
-    <t>11535.0</t>
-  </si>
-  <si>
-    <t>11559.0</t>
-  </si>
-  <si>
-    <t>11573.0</t>
-  </si>
-  <si>
-    <t>11594.0</t>
-  </si>
-  <si>
-    <t>11600.0</t>
-  </si>
-  <si>
-    <t>11622.0</t>
-  </si>
-  <si>
-    <t>11739.0</t>
-  </si>
-  <si>
-    <t>11812.0</t>
-  </si>
-  <si>
-    <t>11850.0</t>
-  </si>
-  <si>
-    <t>11901.0</t>
-  </si>
-  <si>
-    <t>11933.0</t>
-  </si>
-  <si>
-    <t>11982.0</t>
-  </si>
-  <si>
-    <t>11992.0</t>
-  </si>
-  <si>
-    <t>12165.0</t>
-  </si>
-  <si>
-    <t>12166.0</t>
-  </si>
-  <si>
-    <t>12174.0</t>
-  </si>
-  <si>
-    <t>12307.0</t>
-  </si>
-  <si>
-    <t>12378.0</t>
-  </si>
-  <si>
-    <t>12417.0</t>
-  </si>
-  <si>
-    <t>11511.0</t>
-  </si>
-  <si>
-    <t>11512.0</t>
-  </si>
-  <si>
-    <t>11516.0</t>
-  </si>
-  <si>
-    <t>11525.0</t>
-  </si>
-  <si>
-    <t>11526.0</t>
-  </si>
-  <si>
-    <t>11548.0</t>
-  </si>
-  <si>
-    <t>11560.0</t>
-  </si>
-  <si>
-    <t>11574.0</t>
-  </si>
-  <si>
-    <t>11587.0</t>
-  </si>
-  <si>
-    <t>11595.0</t>
-  </si>
-  <si>
-    <t>11636.0</t>
-  </si>
-  <si>
-    <t>11655.0</t>
-  </si>
-  <si>
-    <t>11667.0</t>
-  </si>
-  <si>
-    <t>11668.0</t>
-  </si>
-  <si>
-    <t>11685.0</t>
-  </si>
-  <si>
-    <t>11703.0</t>
-  </si>
-  <si>
-    <t>11704.0</t>
-  </si>
-  <si>
-    <t>11721.0</t>
-  </si>
-  <si>
-    <t>11722.0</t>
-  </si>
-  <si>
-    <t>11740.0</t>
-  </si>
-  <si>
-    <t>11752.0</t>
-  </si>
-  <si>
-    <t>11775.0</t>
-  </si>
-  <si>
-    <t>11802.0</t>
-  </si>
-  <si>
-    <t>11803.0</t>
-  </si>
-  <si>
-    <t>11814.0</t>
-  </si>
-  <si>
-    <t>11813.0</t>
-  </si>
-  <si>
-    <t>11822.0</t>
-  </si>
-  <si>
-    <t>11851.0</t>
-  </si>
-  <si>
-    <t>11873.0</t>
-  </si>
-  <si>
-    <t>11946.0</t>
-  </si>
-  <si>
-    <t>11947.0</t>
-  </si>
-  <si>
-    <t>11967.0</t>
-  </si>
-  <si>
-    <t>11968.0</t>
-  </si>
-  <si>
-    <t>12018.0</t>
-  </si>
-  <si>
-    <t>12029.0</t>
-  </si>
-  <si>
-    <t>12044.0</t>
-  </si>
-  <si>
-    <t>12049.0</t>
-  </si>
-  <si>
-    <t>12071.0</t>
-  </si>
-  <si>
-    <t>12072.0</t>
-  </si>
-  <si>
-    <t>12082.0</t>
-  </si>
-  <si>
-    <t>12093.0</t>
-  </si>
-  <si>
-    <t>12101.0</t>
-  </si>
-  <si>
-    <t>12108.0</t>
-  </si>
-  <si>
-    <t>12109.0</t>
-  </si>
-  <si>
-    <t>12119.0</t>
-  </si>
-  <si>
-    <t>12137.0</t>
-  </si>
-  <si>
-    <t>12150.0</t>
-  </si>
-  <si>
-    <t>12220.0</t>
-  </si>
-  <si>
-    <t>12248.0</t>
-  </si>
-  <si>
-    <t>12261.0</t>
-  </si>
-  <si>
-    <t>12274.0</t>
-  </si>
-  <si>
-    <t>12275.0</t>
-  </si>
-  <si>
-    <t>12291.0</t>
-  </si>
-  <si>
-    <t>12292.0</t>
-  </si>
-  <si>
-    <t>12308.0</t>
-  </si>
-  <si>
-    <t>12341.0</t>
-  </si>
-  <si>
-    <t>12353.0</t>
-  </si>
-  <si>
-    <t>12369.0</t>
-  </si>
-  <si>
-    <t>12379.0</t>
-  </si>
-  <si>
-    <t>12418.0</t>
-  </si>
-  <si>
-    <t>11513.0</t>
-  </si>
-  <si>
-    <t>11514.0</t>
-  </si>
-  <si>
-    <t>11527.0</t>
-  </si>
-  <si>
-    <t>11536.0</t>
-  </si>
-  <si>
-    <t>11561.0</t>
-  </si>
-  <si>
-    <t>11588.0</t>
-  </si>
-  <si>
-    <t>11596.0</t>
-  </si>
-  <si>
-    <t>11604.0</t>
-  </si>
-  <si>
-    <t>11605.0</t>
-  </si>
-  <si>
-    <t>11623.0</t>
-  </si>
-  <si>
-    <t>11624.0</t>
-  </si>
-  <si>
-    <t>11637.0</t>
-  </si>
-  <si>
-    <t>11638.0</t>
-  </si>
-  <si>
-    <t>11656.0</t>
-  </si>
-  <si>
-    <t>11657.0</t>
-  </si>
-  <si>
-    <t>11669.0</t>
-  </si>
-  <si>
-    <t>11670.0</t>
-  </si>
-  <si>
-    <t>11686.0</t>
-  </si>
-  <si>
-    <t>11705.0</t>
-  </si>
-  <si>
-    <t>11723.0</t>
-  </si>
-  <si>
-    <t>11724.0</t>
-  </si>
-  <si>
-    <t>11741.0</t>
-  </si>
-  <si>
-    <t>11753.0</t>
-  </si>
-  <si>
-    <t>11776.0</t>
-  </si>
-  <si>
-    <t>11777.0</t>
-  </si>
-  <si>
-    <t>11778.0</t>
-  </si>
-  <si>
-    <t>11787.0</t>
-  </si>
-  <si>
-    <t>11788.0</t>
-  </si>
-  <si>
-    <t>11804.0</t>
-  </si>
-  <si>
-    <t>11805.0</t>
-  </si>
-  <si>
-    <t>11815.0</t>
-  </si>
-  <si>
-    <t>11818.0</t>
-  </si>
-  <si>
-    <t>11830.0</t>
-  </si>
-  <si>
-    <t>11835.0</t>
-  </si>
-  <si>
-    <t>11836.0</t>
-  </si>
-  <si>
-    <t>11860.0</t>
-  </si>
-  <si>
-    <t>11874.0</t>
-  </si>
-  <si>
-    <t>11887.0</t>
-  </si>
-  <si>
-    <t>11902.0</t>
-  </si>
-  <si>
-    <t>11929.0</t>
-  </si>
-  <si>
-    <t>11948.0</t>
-  </si>
-  <si>
-    <t>11969.0</t>
-  </si>
-  <si>
-    <t>11983.0</t>
-  </si>
-  <si>
-    <t>11993.0</t>
-  </si>
-  <si>
-    <t>12019.0</t>
-  </si>
-  <si>
-    <t>12020.0</t>
-  </si>
-  <si>
-    <t>12030.0</t>
-  </si>
-  <si>
-    <t>12031.0</t>
-  </si>
-  <si>
-    <t>12045.0</t>
-  </si>
-  <si>
-    <t>12046.0</t>
-  </si>
-  <si>
-    <t>12050.0</t>
-  </si>
-  <si>
-    <t>12073.0</t>
-  </si>
-  <si>
-    <t>12074.0</t>
-  </si>
-  <si>
-    <t>12086.0</t>
-  </si>
-  <si>
-    <t>12094.0</t>
-  </si>
-  <si>
-    <t>12102.0</t>
-  </si>
-  <si>
-    <t>12110.0</t>
-  </si>
-  <si>
-    <t>12111.0</t>
-  </si>
-  <si>
-    <t>12120.0</t>
-  </si>
-  <si>
-    <t>12138.0</t>
-  </si>
-  <si>
-    <t>12139.0</t>
-  </si>
-  <si>
-    <t>12151.0</t>
-  </si>
-  <si>
-    <t>12169.0</t>
-  </si>
-  <si>
-    <t>12168.0</t>
-  </si>
-  <si>
-    <t>12170.0</t>
-  </si>
-  <si>
-    <t>12192.0</t>
-  </si>
-  <si>
-    <t>12207.0</t>
-  </si>
-  <si>
-    <t>12221.0</t>
-  </si>
-  <si>
-    <t>12231.0</t>
-  </si>
-  <si>
-    <t>12249.0</t>
-  </si>
-  <si>
-    <t>12250.0</t>
-  </si>
-  <si>
-    <t>12262.0</t>
-  </si>
-  <si>
-    <t>12276.0</t>
-  </si>
-  <si>
-    <t>12293.0</t>
-  </si>
-  <si>
-    <t>12309.0</t>
-  </si>
-  <si>
-    <t>12314.0</t>
-  </si>
-  <si>
-    <t>12325.0</t>
-  </si>
-  <si>
-    <t>12326.0</t>
-  </si>
-  <si>
-    <t>12327.0</t>
-  </si>
-  <si>
-    <t>12342.0</t>
-  </si>
-  <si>
-    <t>12343.0</t>
-  </si>
-  <si>
-    <t>12354.0</t>
-  </si>
-  <si>
-    <t>12355.0</t>
-  </si>
-  <si>
-    <t>12380.0</t>
-  </si>
-  <si>
-    <t>12382.0</t>
-  </si>
-  <si>
-    <t>12391.0</t>
-  </si>
-  <si>
-    <t>12392.0</t>
-  </si>
-  <si>
-    <t>12424.0</t>
-  </si>
-  <si>
-    <t>12425.0</t>
-  </si>
-  <si>
-    <t>12430.0</t>
-  </si>
-  <si>
-    <t>12434.0</t>
+    <t>11687</t>
+  </si>
+  <si>
+    <t>11779</t>
+  </si>
+  <si>
+    <t>11875</t>
+  </si>
+  <si>
+    <t>11496</t>
+  </si>
+  <si>
+    <t>11517</t>
+  </si>
+  <si>
+    <t>11537</t>
+  </si>
+  <si>
+    <t>11562</t>
+  </si>
+  <si>
+    <t>11575</t>
+  </si>
+  <si>
+    <t>11606</t>
+  </si>
+  <si>
+    <t>11611</t>
+  </si>
+  <si>
+    <t>11625</t>
+  </si>
+  <si>
+    <t>11639</t>
+  </si>
+  <si>
+    <t>11658</t>
+  </si>
+  <si>
+    <t>11672</t>
+  </si>
+  <si>
+    <t>11673</t>
+  </si>
+  <si>
+    <t>11671</t>
+  </si>
+  <si>
+    <t>11688</t>
+  </si>
+  <si>
+    <t>11706</t>
+  </si>
+  <si>
+    <t>11725</t>
+  </si>
+  <si>
+    <t>11742</t>
+  </si>
+  <si>
+    <t>11754</t>
+  </si>
+  <si>
+    <t>11789</t>
+  </si>
+  <si>
+    <t>11806</t>
+  </si>
+  <si>
+    <t>11819</t>
+  </si>
+  <si>
+    <t>11820</t>
+  </si>
+  <si>
+    <t>11888</t>
+  </si>
+  <si>
+    <t>11903</t>
+  </si>
+  <si>
+    <t>11911</t>
+  </si>
+  <si>
+    <t>11949</t>
+  </si>
+  <si>
+    <t>11984</t>
+  </si>
+  <si>
+    <t>11985</t>
+  </si>
+  <si>
+    <t>11994</t>
+  </si>
+  <si>
+    <t>12032</t>
+  </si>
+  <si>
+    <t>12051</t>
+  </si>
+  <si>
+    <t>12052</t>
+  </si>
+  <si>
+    <t>12053</t>
+  </si>
+  <si>
+    <t>12087</t>
+  </si>
+  <si>
+    <t>12112</t>
+  </si>
+  <si>
+    <t>12121</t>
+  </si>
+  <si>
+    <t>12122</t>
+  </si>
+  <si>
+    <t>12140</t>
+  </si>
+  <si>
+    <t>12152</t>
+  </si>
+  <si>
+    <t>12154</t>
+  </si>
+  <si>
+    <t>12153</t>
+  </si>
+  <si>
+    <t>12175</t>
+  </si>
+  <si>
+    <t>12179</t>
+  </si>
+  <si>
+    <t>12180</t>
+  </si>
+  <si>
+    <t>12193</t>
+  </si>
+  <si>
+    <t>12222</t>
+  </si>
+  <si>
+    <t>12232</t>
+  </si>
+  <si>
+    <t>12251</t>
+  </si>
+  <si>
+    <t>12263</t>
+  </si>
+  <si>
+    <t>12278</t>
+  </si>
+  <si>
+    <t>12277</t>
+  </si>
+  <si>
+    <t>12315</t>
+  </si>
+  <si>
+    <t>12333</t>
+  </si>
+  <si>
+    <t>12344</t>
+  </si>
+  <si>
+    <t>12356</t>
+  </si>
+  <si>
+    <t>12393</t>
+  </si>
+  <si>
+    <t>12398</t>
+  </si>
+  <si>
+    <t>11497</t>
+  </si>
+  <si>
+    <t>11641</t>
+  </si>
+  <si>
+    <t>11862</t>
+  </si>
+  <si>
+    <t>11951</t>
+  </si>
+  <si>
+    <t>11952</t>
+  </si>
+  <si>
+    <t>12142</t>
+  </si>
+  <si>
+    <t>12223</t>
+  </si>
+  <si>
+    <t>12295</t>
+  </si>
+  <si>
+    <t>12436</t>
+  </si>
+  <si>
+    <t>11518</t>
+  </si>
+  <si>
+    <t>11538</t>
+  </si>
+  <si>
+    <t>11563</t>
+  </si>
+  <si>
+    <t>11576</t>
+  </si>
+  <si>
+    <t>11597</t>
+  </si>
+  <si>
+    <t>11612</t>
+  </si>
+  <si>
+    <t>11626</t>
+  </si>
+  <si>
+    <t>11640</t>
+  </si>
+  <si>
+    <t>11674</t>
+  </si>
+  <si>
+    <t>11689</t>
+  </si>
+  <si>
+    <t>11707</t>
+  </si>
+  <si>
+    <t>11726</t>
+  </si>
+  <si>
+    <t>11743</t>
+  </si>
+  <si>
+    <t>11755</t>
+  </si>
+  <si>
+    <t>11780</t>
+  </si>
+  <si>
+    <t>11823</t>
+  </si>
+  <si>
+    <t>11831</t>
+  </si>
+  <si>
+    <t>11837</t>
+  </si>
+  <si>
+    <t>11852</t>
+  </si>
+  <si>
+    <t>11861</t>
+  </si>
+  <si>
+    <t>11876</t>
+  </si>
+  <si>
+    <t>11889</t>
+  </si>
+  <si>
+    <t>11936</t>
+  </si>
+  <si>
+    <t>11950</t>
+  </si>
+  <si>
+    <t>11970</t>
+  </si>
+  <si>
+    <t>12033</t>
+  </si>
+  <si>
+    <t>12054</t>
+  </si>
+  <si>
+    <t>12075</t>
+  </si>
+  <si>
+    <t>12113</t>
+  </si>
+  <si>
+    <t>12123</t>
+  </si>
+  <si>
+    <t>12141</t>
+  </si>
+  <si>
+    <t>12155</t>
+  </si>
+  <si>
+    <t>12233</t>
+  </si>
+  <si>
+    <t>12264</t>
+  </si>
+  <si>
+    <t>12294</t>
+  </si>
+  <si>
+    <t>12310</t>
+  </si>
+  <si>
+    <t>12316</t>
+  </si>
+  <si>
+    <t>12357</t>
+  </si>
+  <si>
+    <t>12371</t>
+  </si>
+  <si>
+    <t>12383</t>
+  </si>
+  <si>
+    <t>12399</t>
+  </si>
+  <si>
+    <t>12410</t>
+  </si>
+  <si>
+    <t>12420</t>
+  </si>
+  <si>
+    <t>12439</t>
+  </si>
+  <si>
+    <t>12442</t>
+  </si>
+  <si>
+    <t>12443</t>
+  </si>
+  <si>
+    <t>11498</t>
+  </si>
+  <si>
+    <t>11519</t>
+  </si>
+  <si>
+    <t>11539</t>
+  </si>
+  <si>
+    <t>11540</t>
+  </si>
+  <si>
+    <t>11549</t>
+  </si>
+  <si>
+    <t>11564</t>
+  </si>
+  <si>
+    <t>11577</t>
+  </si>
+  <si>
+    <t>11578</t>
+  </si>
+  <si>
+    <t>11607</t>
+  </si>
+  <si>
+    <t>11613</t>
+  </si>
+  <si>
+    <t>11627</t>
+  </si>
+  <si>
+    <t>11642</t>
+  </si>
+  <si>
+    <t>11659</t>
+  </si>
+  <si>
+    <t>11676</t>
+  </si>
+  <si>
+    <t>11675</t>
+  </si>
+  <si>
+    <t>11691</t>
+  </si>
+  <si>
+    <t>11690</t>
+  </si>
+  <si>
+    <t>11692</t>
+  </si>
+  <si>
+    <t>11708</t>
+  </si>
+  <si>
+    <t>11727</t>
+  </si>
+  <si>
+    <t>11744</t>
+  </si>
+  <si>
+    <t>11756</t>
+  </si>
+  <si>
+    <t>11757</t>
+  </si>
+  <si>
+    <t>11790</t>
+  </si>
+  <si>
+    <t>11807</t>
+  </si>
+  <si>
+    <t>11821</t>
+  </si>
+  <si>
+    <t>11832</t>
+  </si>
+  <si>
+    <t>11838</t>
+  </si>
+  <si>
+    <t>11863</t>
+  </si>
+  <si>
+    <t>11890</t>
+  </si>
+  <si>
+    <t>11891</t>
+  </si>
+  <si>
+    <t>11904</t>
+  </si>
+  <si>
+    <t>11912</t>
+  </si>
+  <si>
+    <t>11934</t>
+  </si>
+  <si>
+    <t>11937</t>
+  </si>
+  <si>
+    <t>11953</t>
+  </si>
+  <si>
+    <t>11995</t>
+  </si>
+  <si>
+    <t>12034</t>
+  </si>
+  <si>
+    <t>12055</t>
+  </si>
+  <si>
+    <t>12056</t>
+  </si>
+  <si>
+    <t>12088</t>
+  </si>
+  <si>
+    <t>12124</t>
+  </si>
+  <si>
+    <t>12125</t>
+  </si>
+  <si>
+    <t>12126</t>
+  </si>
+  <si>
+    <t>12143</t>
+  </si>
+  <si>
+    <t>12157</t>
+  </si>
+  <si>
+    <t>12156</t>
+  </si>
+  <si>
+    <t>12176</t>
+  </si>
+  <si>
+    <t>12181</t>
+  </si>
+  <si>
+    <t>12182</t>
+  </si>
+  <si>
+    <t>12183</t>
+  </si>
+  <si>
+    <t>12194</t>
+  </si>
+  <si>
+    <t>12225</t>
+  </si>
+  <si>
+    <t>12224</t>
+  </si>
+  <si>
+    <t>12252</t>
+  </si>
+  <si>
+    <t>12279</t>
+  </si>
+  <si>
+    <t>12311</t>
+  </si>
+  <si>
+    <t>12317</t>
+  </si>
+  <si>
+    <t>12334</t>
+  </si>
+  <si>
+    <t>12346</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>12359</t>
+  </si>
+  <si>
+    <t>12358</t>
+  </si>
+  <si>
+    <t>12372</t>
+  </si>
+  <si>
+    <t>12394</t>
+  </si>
+  <si>
+    <t>12401</t>
+  </si>
+  <si>
+    <t>12400</t>
+  </si>
+  <si>
+    <t>11499</t>
+  </si>
+  <si>
+    <t>11550</t>
+  </si>
+  <si>
+    <t>11579</t>
+  </si>
+  <si>
+    <t>11601</t>
+  </si>
+  <si>
+    <t>11614</t>
+  </si>
+  <si>
+    <t>11615</t>
+  </si>
+  <si>
+    <t>11628</t>
+  </si>
+  <si>
+    <t>11643</t>
+  </si>
+  <si>
+    <t>11645</t>
+  </si>
+  <si>
+    <t>11644</t>
+  </si>
+  <si>
+    <t>11660</t>
+  </si>
+  <si>
+    <t>11662</t>
+  </si>
+  <si>
+    <t>11661</t>
+  </si>
+  <si>
+    <t>11677</t>
+  </si>
+  <si>
+    <t>11678</t>
+  </si>
+  <si>
+    <t>11693</t>
+  </si>
+  <si>
+    <t>11694</t>
+  </si>
+  <si>
+    <t>11709</t>
+  </si>
+  <si>
+    <t>11710</t>
+  </si>
+  <si>
+    <t>11728</t>
+  </si>
+  <si>
+    <t>11729</t>
+  </si>
+  <si>
+    <t>11745</t>
+  </si>
+  <si>
+    <t>11747</t>
+  </si>
+  <si>
+    <t>11746</t>
+  </si>
+  <si>
+    <t>11758</t>
+  </si>
+  <si>
+    <t>11759</t>
+  </si>
+  <si>
+    <t>11781</t>
+  </si>
+  <si>
+    <t>11782</t>
+  </si>
+  <si>
+    <t>11791</t>
+  </si>
+  <si>
+    <t>11792</t>
+  </si>
+  <si>
+    <t>11793</t>
+  </si>
+  <si>
+    <t>11808</t>
+  </si>
+  <si>
+    <t>11809</t>
+  </si>
+  <si>
+    <t>11824</t>
+  </si>
+  <si>
+    <t>11833</t>
+  </si>
+  <si>
+    <t>11834</t>
+  </si>
+  <si>
+    <t>11839</t>
+  </si>
+  <si>
+    <t>11853</t>
+  </si>
+  <si>
+    <t>11864</t>
+  </si>
+  <si>
+    <t>11865</t>
+  </si>
+  <si>
+    <t>11866</t>
+  </si>
+  <si>
+    <t>11867</t>
+  </si>
+  <si>
+    <t>11892</t>
+  </si>
+  <si>
+    <t>11905</t>
+  </si>
+  <si>
+    <t>11913</t>
+  </si>
+  <si>
+    <t>11930</t>
+  </si>
+  <si>
+    <t>11935</t>
+  </si>
+  <si>
+    <t>11954</t>
+  </si>
+  <si>
+    <t>11971</t>
+  </si>
+  <si>
+    <t>11986</t>
+  </si>
+  <si>
+    <t>11997</t>
+  </si>
+  <si>
+    <t>11996</t>
+  </si>
+  <si>
+    <t>11998</t>
+  </si>
+  <si>
+    <t>12007</t>
+  </si>
+  <si>
+    <t>12008</t>
+  </si>
+  <si>
+    <t>12021</t>
+  </si>
+  <si>
+    <t>12035</t>
+  </si>
+  <si>
+    <t>12057</t>
+  </si>
+  <si>
+    <t>12058</t>
+  </si>
+  <si>
+    <t>12059</t>
+  </si>
+  <si>
+    <t>12076</t>
+  </si>
+  <si>
+    <t>12083</t>
+  </si>
+  <si>
+    <t>12089</t>
+  </si>
+  <si>
+    <t>12095</t>
+  </si>
+  <si>
+    <t>12103</t>
+  </si>
+  <si>
+    <t>12114</t>
+  </si>
+  <si>
+    <t>12127</t>
+  </si>
+  <si>
+    <t>12144</t>
+  </si>
+  <si>
+    <t>12145</t>
+  </si>
+  <si>
+    <t>12158</t>
+  </si>
+  <si>
+    <t>12159</t>
+  </si>
+  <si>
+    <t>12160</t>
+  </si>
+  <si>
+    <t>12177</t>
+  </si>
+  <si>
+    <t>12184</t>
+  </si>
+  <si>
+    <t>12185</t>
+  </si>
+  <si>
+    <t>12195</t>
+  </si>
+  <si>
+    <t>12197</t>
+  </si>
+  <si>
+    <t>12196</t>
+  </si>
+  <si>
+    <t>12208</t>
+  </si>
+  <si>
+    <t>12210</t>
+  </si>
+  <si>
+    <t>12209</t>
+  </si>
+  <si>
+    <t>12226</t>
+  </si>
+  <si>
+    <t>12234</t>
+  </si>
+  <si>
+    <t>12253</t>
+  </si>
+  <si>
+    <t>12254</t>
+  </si>
+  <si>
+    <t>12265</t>
+  </si>
+  <si>
+    <t>12280</t>
+  </si>
+  <si>
+    <t>12282</t>
+  </si>
+  <si>
+    <t>12281</t>
+  </si>
+  <si>
+    <t>12296</t>
+  </si>
+  <si>
+    <t>12297</t>
+  </si>
+  <si>
+    <t>12312</t>
+  </si>
+  <si>
+    <t>12318</t>
+  </si>
+  <si>
+    <t>12328</t>
+  </si>
+  <si>
+    <t>12335</t>
+  </si>
+  <si>
+    <t>12347</t>
+  </si>
+  <si>
+    <t>12360</t>
+  </si>
+  <si>
+    <t>12361</t>
+  </si>
+  <si>
+    <t>12370</t>
+  </si>
+  <si>
+    <t>12381</t>
+  </si>
+  <si>
+    <t>12384</t>
+  </si>
+  <si>
+    <t>12403</t>
+  </si>
+  <si>
+    <t>12402</t>
+  </si>
+  <si>
+    <t>12404</t>
+  </si>
+  <si>
+    <t>12411</t>
+  </si>
+  <si>
+    <t>12412</t>
+  </si>
+  <si>
+    <t>12421</t>
+  </si>
+  <si>
+    <t>12426</t>
+  </si>
+  <si>
+    <t>12429</t>
+  </si>
+  <si>
+    <t>12431</t>
+  </si>
+  <si>
+    <t>12435</t>
+  </si>
+  <si>
+    <t>12438</t>
+  </si>
+  <si>
+    <t>12440</t>
+  </si>
+  <si>
+    <t>12441</t>
+  </si>
+  <si>
+    <t>11520</t>
+  </si>
+  <si>
+    <t>11528</t>
+  </si>
+  <si>
+    <t>11529</t>
+  </si>
+  <si>
+    <t>11530</t>
+  </si>
+  <si>
+    <t>11565</t>
+  </si>
+  <si>
+    <t>11590</t>
+  </si>
+  <si>
+    <t>11589</t>
+  </si>
+  <si>
+    <t>11629</t>
+  </si>
+  <si>
+    <t>11646</t>
+  </si>
+  <si>
+    <t>11647</t>
+  </si>
+  <si>
+    <t>11663</t>
+  </si>
+  <si>
+    <t>11679</t>
+  </si>
+  <si>
+    <t>11794</t>
+  </si>
+  <si>
+    <t>11840</t>
+  </si>
+  <si>
+    <t>11841</t>
+  </si>
+  <si>
+    <t>11842</t>
+  </si>
+  <si>
+    <t>11938</t>
+  </si>
+  <si>
+    <t>11987</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>12009</t>
+  </si>
+  <si>
+    <t>12022</t>
+  </si>
+  <si>
+    <t>12060</t>
+  </si>
+  <si>
+    <t>12077</t>
+  </si>
+  <si>
+    <t>12090</t>
+  </si>
+  <si>
+    <t>12115</t>
+  </si>
+  <si>
+    <t>12128</t>
+  </si>
+  <si>
+    <t>12146</t>
+  </si>
+  <si>
+    <t>12198</t>
+  </si>
+  <si>
+    <t>12236</t>
+  </si>
+  <si>
+    <t>12235</t>
+  </si>
+  <si>
+    <t>12266</t>
+  </si>
+  <si>
+    <t>12283</t>
+  </si>
+  <si>
+    <t>12298</t>
+  </si>
+  <si>
+    <t>12319</t>
+  </si>
+  <si>
+    <t>12395</t>
+  </si>
+  <si>
+    <t>11500</t>
+  </si>
+  <si>
+    <t>11580</t>
+  </si>
+  <si>
+    <t>11591</t>
+  </si>
+  <si>
+    <t>11602</t>
+  </si>
+  <si>
+    <t>11877</t>
+  </si>
+  <si>
+    <t>11931</t>
+  </si>
+  <si>
+    <t>11955</t>
+  </si>
+  <si>
+    <t>11972</t>
+  </si>
+  <si>
+    <t>12010</t>
+  </si>
+  <si>
+    <t>12147</t>
+  </si>
+  <si>
+    <t>12267</t>
+  </si>
+  <si>
+    <t>12437</t>
+  </si>
+  <si>
+    <t>11680</t>
+  </si>
+  <si>
+    <t>11711</t>
+  </si>
+  <si>
+    <t>11712</t>
+  </si>
+  <si>
+    <t>11825</t>
+  </si>
+  <si>
+    <t>11854</t>
+  </si>
+  <si>
+    <t>11868</t>
+  </si>
+  <si>
+    <t>11914</t>
+  </si>
+  <si>
+    <t>11916</t>
+  </si>
+  <si>
+    <t>11915</t>
+  </si>
+  <si>
+    <t>11956</t>
+  </si>
+  <si>
+    <t>11957</t>
+  </si>
+  <si>
+    <t>11988</t>
+  </si>
+  <si>
+    <t>12011</t>
+  </si>
+  <si>
+    <t>12023</t>
+  </si>
+  <si>
+    <t>12061</t>
+  </si>
+  <si>
+    <t>12062</t>
+  </si>
+  <si>
+    <t>12063</t>
+  </si>
+  <si>
+    <t>12064</t>
+  </si>
+  <si>
+    <t>12129</t>
+  </si>
+  <si>
+    <t>12130</t>
+  </si>
+  <si>
+    <t>12131</t>
+  </si>
+  <si>
+    <t>12148</t>
+  </si>
+  <si>
+    <t>12149</t>
+  </si>
+  <si>
+    <t>12162</t>
+  </si>
+  <si>
+    <t>12161</t>
+  </si>
+  <si>
+    <t>12163</t>
+  </si>
+  <si>
+    <t>12171</t>
+  </si>
+  <si>
+    <t>12172</t>
+  </si>
+  <si>
+    <t>12173</t>
+  </si>
+  <si>
+    <t>12200</t>
+  </si>
+  <si>
+    <t>12199</t>
+  </si>
+  <si>
+    <t>12237</t>
+  </si>
+  <si>
+    <t>12238</t>
+  </si>
+  <si>
+    <t>12284</t>
+  </si>
+  <si>
+    <t>12300</t>
+  </si>
+  <si>
+    <t>12299</t>
+  </si>
+  <si>
+    <t>12348</t>
+  </si>
+  <si>
+    <t>12373</t>
+  </si>
+  <si>
+    <t>12374</t>
+  </si>
+  <si>
+    <t>12375</t>
+  </si>
+  <si>
+    <t>12386</t>
+  </si>
+  <si>
+    <t>12385</t>
+  </si>
+  <si>
+    <t>12405</t>
+  </si>
+  <si>
+    <t>12413</t>
+  </si>
+  <si>
+    <t>12422</t>
+  </si>
+  <si>
+    <t>11502</t>
+  </si>
+  <si>
+    <t>11505</t>
+  </si>
+  <si>
+    <t>11503</t>
+  </si>
+  <si>
+    <t>11504</t>
+  </si>
+  <si>
+    <t>11515</t>
+  </si>
+  <si>
+    <t>11521</t>
+  </si>
+  <si>
+    <t>11522</t>
+  </si>
+  <si>
+    <t>11531</t>
+  </si>
+  <si>
+    <t>11541</t>
+  </si>
+  <si>
+    <t>11543</t>
+  </si>
+  <si>
+    <t>11542</t>
+  </si>
+  <si>
+    <t>11551</t>
+  </si>
+  <si>
+    <t>11552</t>
+  </si>
+  <si>
+    <t>11567</t>
+  </si>
+  <si>
+    <t>11568</t>
+  </si>
+  <si>
+    <t>11566</t>
+  </si>
+  <si>
+    <t>11581</t>
+  </si>
+  <si>
+    <t>11582</t>
+  </si>
+  <si>
+    <t>11598</t>
+  </si>
+  <si>
+    <t>11603</t>
+  </si>
+  <si>
+    <t>11616</t>
+  </si>
+  <si>
+    <t>11617</t>
+  </si>
+  <si>
+    <t>11630</t>
+  </si>
+  <si>
+    <t>11648</t>
+  </si>
+  <si>
+    <t>11649</t>
+  </si>
+  <si>
+    <t>11664</t>
+  </si>
+  <si>
+    <t>11665</t>
+  </si>
+  <si>
+    <t>11681</t>
+  </si>
+  <si>
+    <t>11695</t>
+  </si>
+  <si>
+    <t>11696</t>
+  </si>
+  <si>
+    <t>11713</t>
+  </si>
+  <si>
+    <t>11714</t>
+  </si>
+  <si>
+    <t>11715</t>
+  </si>
+  <si>
+    <t>11716</t>
+  </si>
+  <si>
+    <t>11730</t>
+  </si>
+  <si>
+    <t>11731</t>
+  </si>
+  <si>
+    <t>11732</t>
+  </si>
+  <si>
+    <t>11748</t>
+  </si>
+  <si>
+    <t>11749</t>
+  </si>
+  <si>
+    <t>11760</t>
+  </si>
+  <si>
+    <t>11761</t>
+  </si>
+  <si>
+    <t>11762</t>
+  </si>
+  <si>
+    <t>11763</t>
+  </si>
+  <si>
+    <t>11764</t>
+  </si>
+  <si>
+    <t>11783</t>
+  </si>
+  <si>
+    <t>11795</t>
+  </si>
+  <si>
+    <t>11796</t>
+  </si>
+  <si>
+    <t>11797</t>
+  </si>
+  <si>
+    <t>11798</t>
+  </si>
+  <si>
+    <t>11810</t>
+  </si>
+  <si>
+    <t>11811</t>
+  </si>
+  <si>
+    <t>11816</t>
+  </si>
+  <si>
+    <t>11826</t>
+  </si>
+  <si>
+    <t>11843</t>
+  </si>
+  <si>
+    <t>11844</t>
+  </si>
+  <si>
+    <t>11855</t>
+  </si>
+  <si>
+    <t>11869</t>
+  </si>
+  <si>
+    <t>11879</t>
+  </si>
+  <si>
+    <t>11878</t>
+  </si>
+  <si>
+    <t>11881</t>
+  </si>
+  <si>
+    <t>11880</t>
+  </si>
+  <si>
+    <t>11893</t>
+  </si>
+  <si>
+    <t>11906</t>
+  </si>
+  <si>
+    <t>11917</t>
+  </si>
+  <si>
+    <t>11918</t>
+  </si>
+  <si>
+    <t>11920</t>
+  </si>
+  <si>
+    <t>11921</t>
+  </si>
+  <si>
+    <t>11919</t>
+  </si>
+  <si>
+    <t>11932</t>
+  </si>
+  <si>
+    <t>11939</t>
+  </si>
+  <si>
+    <t>11940</t>
+  </si>
+  <si>
+    <t>11958</t>
+  </si>
+  <si>
+    <t>11960</t>
+  </si>
+  <si>
+    <t>11974</t>
+  </si>
+  <si>
+    <t>11973</t>
+  </si>
+  <si>
+    <t>11989</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>12001</t>
+  </si>
+  <si>
+    <t>12024</t>
+  </si>
+  <si>
+    <t>12036</t>
+  </si>
+  <si>
+    <t>12037</t>
+  </si>
+  <si>
+    <t>12066</t>
+  </si>
+  <si>
+    <t>12065</t>
+  </si>
+  <si>
+    <t>12078</t>
+  </si>
+  <si>
+    <t>12096</t>
+  </si>
+  <si>
+    <t>12104</t>
+  </si>
+  <si>
+    <t>12132</t>
+  </si>
+  <si>
+    <t>12164</t>
+  </si>
+  <si>
+    <t>12201</t>
+  </si>
+  <si>
+    <t>12202</t>
+  </si>
+  <si>
+    <t>12211</t>
+  </si>
+  <si>
+    <t>12212</t>
+  </si>
+  <si>
+    <t>12213</t>
+  </si>
+  <si>
+    <t>12227</t>
+  </si>
+  <si>
+    <t>12239</t>
+  </si>
+  <si>
+    <t>12240</t>
+  </si>
+  <si>
+    <t>12241</t>
+  </si>
+  <si>
+    <t>12257</t>
+  </si>
+  <si>
+    <t>12255</t>
+  </si>
+  <si>
+    <t>12256</t>
+  </si>
+  <si>
+    <t>12268</t>
+  </si>
+  <si>
+    <t>12285</t>
+  </si>
+  <si>
+    <t>12286</t>
+  </si>
+  <si>
+    <t>12287</t>
+  </si>
+  <si>
+    <t>12301</t>
+  </si>
+  <si>
+    <t>12313</t>
+  </si>
+  <si>
+    <t>12321</t>
+  </si>
+  <si>
+    <t>12336</t>
+  </si>
+  <si>
+    <t>12349</t>
+  </si>
+  <si>
+    <t>12362</t>
+  </si>
+  <si>
+    <t>12363</t>
+  </si>
+  <si>
+    <t>12387</t>
+  </si>
+  <si>
+    <t>12419</t>
+  </si>
+  <si>
+    <t>12428</t>
+  </si>
+  <si>
+    <t>12427</t>
+  </si>
+  <si>
+    <t>12432</t>
+  </si>
+  <si>
+    <t>11506</t>
+  </si>
+  <si>
+    <t>11523</t>
+  </si>
+  <si>
+    <t>11532</t>
+  </si>
+  <si>
+    <t>11544</t>
+  </si>
+  <si>
+    <t>11553</t>
+  </si>
+  <si>
+    <t>11569</t>
+  </si>
+  <si>
+    <t>11583</t>
+  </si>
+  <si>
+    <t>11608</t>
+  </si>
+  <si>
+    <t>11609</t>
+  </si>
+  <si>
+    <t>11733</t>
+  </si>
+  <si>
+    <t>11734</t>
+  </si>
+  <si>
+    <t>11765</t>
+  </si>
+  <si>
+    <t>11766</t>
+  </si>
+  <si>
+    <t>11767</t>
+  </si>
+  <si>
+    <t>11768</t>
+  </si>
+  <si>
+    <t>11769</t>
+  </si>
+  <si>
+    <t>11799</t>
+  </si>
+  <si>
+    <t>11922</t>
+  </si>
+  <si>
+    <t>11941</t>
+  </si>
+  <si>
+    <t>11961</t>
+  </si>
+  <si>
+    <t>11975</t>
+  </si>
+  <si>
+    <t>12002</t>
+  </si>
+  <si>
+    <t>12178</t>
+  </si>
+  <si>
+    <t>12187</t>
+  </si>
+  <si>
+    <t>12188</t>
+  </si>
+  <si>
+    <t>12214</t>
+  </si>
+  <si>
+    <t>12414</t>
+  </si>
+  <si>
+    <t>11508</t>
+  </si>
+  <si>
+    <t>11509</t>
+  </si>
+  <si>
+    <t>11507</t>
+  </si>
+  <si>
+    <t>11524</t>
+  </si>
+  <si>
+    <t>11533</t>
+  </si>
+  <si>
+    <t>11534</t>
+  </si>
+  <si>
+    <t>11545</t>
+  </si>
+  <si>
+    <t>11547</t>
+  </si>
+  <si>
+    <t>11546</t>
+  </si>
+  <si>
+    <t>11555</t>
+  </si>
+  <si>
+    <t>11554</t>
+  </si>
+  <si>
+    <t>11557</t>
+  </si>
+  <si>
+    <t>11556</t>
+  </si>
+  <si>
+    <t>11558</t>
+  </si>
+  <si>
+    <t>11571</t>
+  </si>
+  <si>
+    <t>11570</t>
+  </si>
+  <si>
+    <t>11572</t>
+  </si>
+  <si>
+    <t>11585</t>
+  </si>
+  <si>
+    <t>11584</t>
+  </si>
+  <si>
+    <t>11586</t>
+  </si>
+  <si>
+    <t>11592</t>
+  </si>
+  <si>
+    <t>11593</t>
+  </si>
+  <si>
+    <t>11599</t>
+  </si>
+  <si>
+    <t>11610</t>
+  </si>
+  <si>
+    <t>11618</t>
+  </si>
+  <si>
+    <t>11620</t>
+  </si>
+  <si>
+    <t>11619</t>
+  </si>
+  <si>
+    <t>11621</t>
+  </si>
+  <si>
+    <t>11631</t>
+  </si>
+  <si>
+    <t>11632</t>
+  </si>
+  <si>
+    <t>11634</t>
+  </si>
+  <si>
+    <t>11633</t>
+  </si>
+  <si>
+    <t>11635</t>
+  </si>
+  <si>
+    <t>11650</t>
+  </si>
+  <si>
+    <t>11651</t>
+  </si>
+  <si>
+    <t>11652</t>
+  </si>
+  <si>
+    <t>11653</t>
+  </si>
+  <si>
+    <t>11666</t>
+  </si>
+  <si>
+    <t>11682</t>
+  </si>
+  <si>
+    <t>11683</t>
+  </si>
+  <si>
+    <t>11684</t>
+  </si>
+  <si>
+    <t>11697</t>
+  </si>
+  <si>
+    <t>11698</t>
+  </si>
+  <si>
+    <t>11699</t>
+  </si>
+  <si>
+    <t>11700</t>
+  </si>
+  <si>
+    <t>11701</t>
+  </si>
+  <si>
+    <t>11717</t>
+  </si>
+  <si>
+    <t>11719</t>
+  </si>
+  <si>
+    <t>11718</t>
+  </si>
+  <si>
+    <t>11720</t>
+  </si>
+  <si>
+    <t>11735</t>
+  </si>
+  <si>
+    <t>11736</t>
+  </si>
+  <si>
+    <t>11737</t>
+  </si>
+  <si>
+    <t>11738</t>
+  </si>
+  <si>
+    <t>11750</t>
+  </si>
+  <si>
+    <t>11751</t>
+  </si>
+  <si>
+    <t>11771</t>
+  </si>
+  <si>
+    <t>11772</t>
+  </si>
+  <si>
+    <t>11770</t>
+  </si>
+  <si>
+    <t>11773</t>
+  </si>
+  <si>
+    <t>11784</t>
+  </si>
+  <si>
+    <t>11785</t>
+  </si>
+  <si>
+    <t>11800</t>
+  </si>
+  <si>
+    <t>11801</t>
+  </si>
+  <si>
+    <t>11817</t>
+  </si>
+  <si>
+    <t>11827</t>
+  </si>
+  <si>
+    <t>11828</t>
+  </si>
+  <si>
+    <t>11829</t>
+  </si>
+  <si>
+    <t>11845</t>
+  </si>
+  <si>
+    <t>11847</t>
+  </si>
+  <si>
+    <t>11846</t>
+  </si>
+  <si>
+    <t>11848</t>
+  </si>
+  <si>
+    <t>11849</t>
+  </si>
+  <si>
+    <t>11857</t>
+  </si>
+  <si>
+    <t>11856</t>
+  </si>
+  <si>
+    <t>11858</t>
+  </si>
+  <si>
+    <t>11870</t>
+  </si>
+  <si>
+    <t>11871</t>
+  </si>
+  <si>
+    <t>11872</t>
+  </si>
+  <si>
+    <t>11883</t>
+  </si>
+  <si>
+    <t>11884</t>
+  </si>
+  <si>
+    <t>11882</t>
+  </si>
+  <si>
+    <t>11885</t>
+  </si>
+  <si>
+    <t>11894</t>
+  </si>
+  <si>
+    <t>11896</t>
+  </si>
+  <si>
+    <t>11897</t>
+  </si>
+  <si>
+    <t>11898</t>
+  </si>
+  <si>
+    <t>11895</t>
+  </si>
+  <si>
+    <t>11899</t>
+  </si>
+  <si>
+    <t>11907</t>
+  </si>
+  <si>
+    <t>11908</t>
+  </si>
+  <si>
+    <t>11909</t>
+  </si>
+  <si>
+    <t>11910</t>
+  </si>
+  <si>
+    <t>11924</t>
+  </si>
+  <si>
+    <t>11925</t>
+  </si>
+  <si>
+    <t>11926</t>
+  </si>
+  <si>
+    <t>11923</t>
+  </si>
+  <si>
+    <t>11927</t>
+  </si>
+  <si>
+    <t>11928</t>
+  </si>
+  <si>
+    <t>11942</t>
+  </si>
+  <si>
+    <t>11943</t>
+  </si>
+  <si>
+    <t>11944</t>
+  </si>
+  <si>
+    <t>11945</t>
+  </si>
+  <si>
+    <t>11963</t>
+  </si>
+  <si>
+    <t>11964</t>
+  </si>
+  <si>
+    <t>11962</t>
+  </si>
+  <si>
+    <t>11965</t>
+  </si>
+  <si>
+    <t>11966</t>
+  </si>
+  <si>
+    <t>11977</t>
+  </si>
+  <si>
+    <t>11978</t>
+  </si>
+  <si>
+    <t>11976</t>
+  </si>
+  <si>
+    <t>11979</t>
+  </si>
+  <si>
+    <t>11980</t>
+  </si>
+  <si>
+    <t>11990</t>
+  </si>
+  <si>
+    <t>11991</t>
+  </si>
+  <si>
+    <t>12003</t>
+  </si>
+  <si>
+    <t>12004</t>
+  </si>
+  <si>
+    <t>12005</t>
+  </si>
+  <si>
+    <t>12006</t>
+  </si>
+  <si>
+    <t>12012</t>
+  </si>
+  <si>
+    <t>12014</t>
+  </si>
+  <si>
+    <t>12013</t>
+  </si>
+  <si>
+    <t>12015</t>
+  </si>
+  <si>
+    <t>12016</t>
+  </si>
+  <si>
+    <t>12025</t>
+  </si>
+  <si>
+    <t>12027</t>
+  </si>
+  <si>
+    <t>12026</t>
+  </si>
+  <si>
+    <t>12028</t>
+  </si>
+  <si>
+    <t>12038</t>
+  </si>
+  <si>
+    <t>12040</t>
+  </si>
+  <si>
+    <t>12041</t>
+  </si>
+  <si>
+    <t>12039</t>
+  </si>
+  <si>
+    <t>12042</t>
+  </si>
+  <si>
+    <t>12043</t>
+  </si>
+  <si>
+    <t>12047</t>
+  </si>
+  <si>
+    <t>12048</t>
+  </si>
+  <si>
+    <t>12067</t>
+  </si>
+  <si>
+    <t>12068</t>
+  </si>
+  <si>
+    <t>12069</t>
+  </si>
+  <si>
+    <t>12070</t>
+  </si>
+  <si>
+    <t>12079</t>
+  </si>
+  <si>
+    <t>12080</t>
+  </si>
+  <si>
+    <t>12081</t>
+  </si>
+  <si>
+    <t>12084</t>
+  </si>
+  <si>
+    <t>12085</t>
+  </si>
+  <si>
+    <t>12091</t>
+  </si>
+  <si>
+    <t>12097</t>
+  </si>
+  <si>
+    <t>12098</t>
+  </si>
+  <si>
+    <t>12099</t>
+  </si>
+  <si>
+    <t>12105</t>
+  </si>
+  <si>
+    <t>12106</t>
+  </si>
+  <si>
+    <t>12107</t>
+  </si>
+  <si>
+    <t>12116</t>
+  </si>
+  <si>
+    <t>12117</t>
+  </si>
+  <si>
+    <t>12118</t>
+  </si>
+  <si>
+    <t>12134</t>
+  </si>
+  <si>
+    <t>12135</t>
+  </si>
+  <si>
+    <t>12133</t>
+  </si>
+  <si>
+    <t>12136</t>
+  </si>
+  <si>
+    <t>12189</t>
+  </si>
+  <si>
+    <t>12190</t>
+  </si>
+  <si>
+    <t>12191</t>
+  </si>
+  <si>
+    <t>12203</t>
+  </si>
+  <si>
+    <t>12205</t>
+  </si>
+  <si>
+    <t>12204</t>
+  </si>
+  <si>
+    <t>12206</t>
+  </si>
+  <si>
+    <t>12215</t>
+  </si>
+  <si>
+    <t>12216</t>
+  </si>
+  <si>
+    <t>12218</t>
+  </si>
+  <si>
+    <t>12217</t>
+  </si>
+  <si>
+    <t>12219</t>
+  </si>
+  <si>
+    <t>12229</t>
+  </si>
+  <si>
+    <t>12228</t>
+  </si>
+  <si>
+    <t>12230</t>
+  </si>
+  <si>
+    <t>12242</t>
+  </si>
+  <si>
+    <t>12244</t>
+  </si>
+  <si>
+    <t>12245</t>
+  </si>
+  <si>
+    <t>12243</t>
+  </si>
+  <si>
+    <t>12246</t>
+  </si>
+  <si>
+    <t>12247</t>
+  </si>
+  <si>
+    <t>12258</t>
+  </si>
+  <si>
+    <t>12260</t>
+  </si>
+  <si>
+    <t>12259</t>
+  </si>
+  <si>
+    <t>12269</t>
+  </si>
+  <si>
+    <t>12271</t>
+  </si>
+  <si>
+    <t>12270</t>
+  </si>
+  <si>
+    <t>12272</t>
+  </si>
+  <si>
+    <t>12273</t>
+  </si>
+  <si>
+    <t>12289</t>
+  </si>
+  <si>
+    <t>12288</t>
+  </si>
+  <si>
+    <t>12290</t>
+  </si>
+  <si>
+    <t>12302</t>
+  </si>
+  <si>
+    <t>12304</t>
+  </si>
+  <si>
+    <t>12303</t>
+  </si>
+  <si>
+    <t>12305</t>
+  </si>
+  <si>
+    <t>12323</t>
+  </si>
+  <si>
+    <t>12322</t>
+  </si>
+  <si>
+    <t>12324</t>
+  </si>
+  <si>
+    <t>12329</t>
+  </si>
+  <si>
+    <t>12330</t>
+  </si>
+  <si>
+    <t>12331</t>
+  </si>
+  <si>
+    <t>12337</t>
+  </si>
+  <si>
+    <t>12339</t>
+  </si>
+  <si>
+    <t>12338</t>
+  </si>
+  <si>
+    <t>12340</t>
+  </si>
+  <si>
+    <t>12350</t>
+  </si>
+  <si>
+    <t>12351</t>
+  </si>
+  <si>
+    <t>12352</t>
+  </si>
+  <si>
+    <t>12364</t>
+  </si>
+  <si>
+    <t>12365</t>
+  </si>
+  <si>
+    <t>12366</t>
+  </si>
+  <si>
+    <t>12367</t>
+  </si>
+  <si>
+    <t>12368</t>
+  </si>
+  <si>
+    <t>12376</t>
+  </si>
+  <si>
+    <t>12377</t>
+  </si>
+  <si>
+    <t>12388</t>
+  </si>
+  <si>
+    <t>12389</t>
+  </si>
+  <si>
+    <t>12390</t>
+  </si>
+  <si>
+    <t>12396</t>
+  </si>
+  <si>
+    <t>12397</t>
+  </si>
+  <si>
+    <t>12406</t>
+  </si>
+  <si>
+    <t>12407</t>
+  </si>
+  <si>
+    <t>12408</t>
+  </si>
+  <si>
+    <t>12415</t>
+  </si>
+  <si>
+    <t>12416</t>
+  </si>
+  <si>
+    <t>12444</t>
+  </si>
+  <si>
+    <t>11510</t>
+  </si>
+  <si>
+    <t>11774</t>
+  </si>
+  <si>
+    <t>11859</t>
+  </si>
+  <si>
+    <t>11886</t>
+  </si>
+  <si>
+    <t>12017</t>
+  </si>
+  <si>
+    <t>12409</t>
+  </si>
+  <si>
+    <t>12433</t>
+  </si>
+  <si>
+    <t>11654</t>
+  </si>
+  <si>
+    <t>11981</t>
+  </si>
+  <si>
+    <t>12100</t>
+  </si>
+  <si>
+    <t>11702</t>
+  </si>
+  <si>
+    <t>11900</t>
+  </si>
+  <si>
+    <t>12092</t>
+  </si>
+  <si>
+    <t>12306</t>
+  </si>
+  <si>
+    <t>12332</t>
+  </si>
+  <si>
+    <t>11535</t>
+  </si>
+  <si>
+    <t>11559</t>
+  </si>
+  <si>
+    <t>11573</t>
+  </si>
+  <si>
+    <t>11594</t>
+  </si>
+  <si>
+    <t>11600</t>
+  </si>
+  <si>
+    <t>11622</t>
+  </si>
+  <si>
+    <t>11739</t>
+  </si>
+  <si>
+    <t>11812</t>
+  </si>
+  <si>
+    <t>11850</t>
+  </si>
+  <si>
+    <t>11901</t>
+  </si>
+  <si>
+    <t>11933</t>
+  </si>
+  <si>
+    <t>11982</t>
+  </si>
+  <si>
+    <t>11992</t>
+  </si>
+  <si>
+    <t>12165</t>
+  </si>
+  <si>
+    <t>12166</t>
+  </si>
+  <si>
+    <t>12174</t>
+  </si>
+  <si>
+    <t>12307</t>
+  </si>
+  <si>
+    <t>12378</t>
+  </si>
+  <si>
+    <t>12417</t>
+  </si>
+  <si>
+    <t>11511</t>
+  </si>
+  <si>
+    <t>11512</t>
+  </si>
+  <si>
+    <t>11516</t>
+  </si>
+  <si>
+    <t>11525</t>
+  </si>
+  <si>
+    <t>11526</t>
+  </si>
+  <si>
+    <t>11548</t>
+  </si>
+  <si>
+    <t>11560</t>
+  </si>
+  <si>
+    <t>11574</t>
+  </si>
+  <si>
+    <t>11587</t>
+  </si>
+  <si>
+    <t>11595</t>
+  </si>
+  <si>
+    <t>11636</t>
+  </si>
+  <si>
+    <t>11655</t>
+  </si>
+  <si>
+    <t>11667</t>
+  </si>
+  <si>
+    <t>11668</t>
+  </si>
+  <si>
+    <t>11685</t>
+  </si>
+  <si>
+    <t>11703</t>
+  </si>
+  <si>
+    <t>11704</t>
+  </si>
+  <si>
+    <t>11721</t>
+  </si>
+  <si>
+    <t>11722</t>
+  </si>
+  <si>
+    <t>11740</t>
+  </si>
+  <si>
+    <t>11752</t>
+  </si>
+  <si>
+    <t>11775</t>
+  </si>
+  <si>
+    <t>11802</t>
+  </si>
+  <si>
+    <t>11803</t>
+  </si>
+  <si>
+    <t>11814</t>
+  </si>
+  <si>
+    <t>11813</t>
+  </si>
+  <si>
+    <t>11822</t>
+  </si>
+  <si>
+    <t>11851</t>
+  </si>
+  <si>
+    <t>11873</t>
+  </si>
+  <si>
+    <t>11946</t>
+  </si>
+  <si>
+    <t>11947</t>
+  </si>
+  <si>
+    <t>11967</t>
+  </si>
+  <si>
+    <t>11968</t>
+  </si>
+  <si>
+    <t>12018</t>
+  </si>
+  <si>
+    <t>12029</t>
+  </si>
+  <si>
+    <t>12044</t>
+  </si>
+  <si>
+    <t>12049</t>
+  </si>
+  <si>
+    <t>12071</t>
+  </si>
+  <si>
+    <t>12072</t>
+  </si>
+  <si>
+    <t>12082</t>
+  </si>
+  <si>
+    <t>12093</t>
+  </si>
+  <si>
+    <t>12101</t>
+  </si>
+  <si>
+    <t>12108</t>
+  </si>
+  <si>
+    <t>12109</t>
+  </si>
+  <si>
+    <t>12119</t>
+  </si>
+  <si>
+    <t>12137</t>
+  </si>
+  <si>
+    <t>12150</t>
+  </si>
+  <si>
+    <t>12220</t>
+  </si>
+  <si>
+    <t>12248</t>
+  </si>
+  <si>
+    <t>12261</t>
+  </si>
+  <si>
+    <t>12274</t>
+  </si>
+  <si>
+    <t>12275</t>
+  </si>
+  <si>
+    <t>12291</t>
+  </si>
+  <si>
+    <t>12292</t>
+  </si>
+  <si>
+    <t>12308</t>
+  </si>
+  <si>
+    <t>12341</t>
+  </si>
+  <si>
+    <t>12353</t>
+  </si>
+  <si>
+    <t>12369</t>
+  </si>
+  <si>
+    <t>12379</t>
+  </si>
+  <si>
+    <t>12418</t>
+  </si>
+  <si>
+    <t>11513</t>
+  </si>
+  <si>
+    <t>11514</t>
+  </si>
+  <si>
+    <t>11527</t>
+  </si>
+  <si>
+    <t>11536</t>
+  </si>
+  <si>
+    <t>11561</t>
+  </si>
+  <si>
+    <t>11588</t>
+  </si>
+  <si>
+    <t>11596</t>
+  </si>
+  <si>
+    <t>11604</t>
+  </si>
+  <si>
+    <t>11605</t>
+  </si>
+  <si>
+    <t>11623</t>
+  </si>
+  <si>
+    <t>11624</t>
+  </si>
+  <si>
+    <t>11637</t>
+  </si>
+  <si>
+    <t>11638</t>
+  </si>
+  <si>
+    <t>11656</t>
+  </si>
+  <si>
+    <t>11657</t>
+  </si>
+  <si>
+    <t>11669</t>
+  </si>
+  <si>
+    <t>11670</t>
+  </si>
+  <si>
+    <t>11686</t>
+  </si>
+  <si>
+    <t>11705</t>
+  </si>
+  <si>
+    <t>11723</t>
+  </si>
+  <si>
+    <t>11724</t>
+  </si>
+  <si>
+    <t>11741</t>
+  </si>
+  <si>
+    <t>11753</t>
+  </si>
+  <si>
+    <t>11776</t>
+  </si>
+  <si>
+    <t>11777</t>
+  </si>
+  <si>
+    <t>11778</t>
+  </si>
+  <si>
+    <t>11787</t>
+  </si>
+  <si>
+    <t>11788</t>
+  </si>
+  <si>
+    <t>11804</t>
+  </si>
+  <si>
+    <t>11805</t>
+  </si>
+  <si>
+    <t>11815</t>
+  </si>
+  <si>
+    <t>11818</t>
+  </si>
+  <si>
+    <t>11830</t>
+  </si>
+  <si>
+    <t>11835</t>
+  </si>
+  <si>
+    <t>11836</t>
+  </si>
+  <si>
+    <t>11860</t>
+  </si>
+  <si>
+    <t>11874</t>
+  </si>
+  <si>
+    <t>11887</t>
+  </si>
+  <si>
+    <t>11902</t>
+  </si>
+  <si>
+    <t>11929</t>
+  </si>
+  <si>
+    <t>11948</t>
+  </si>
+  <si>
+    <t>11969</t>
+  </si>
+  <si>
+    <t>11983</t>
+  </si>
+  <si>
+    <t>11993</t>
+  </si>
+  <si>
+    <t>12019</t>
+  </si>
+  <si>
+    <t>12020</t>
+  </si>
+  <si>
+    <t>12030</t>
+  </si>
+  <si>
+    <t>12031</t>
+  </si>
+  <si>
+    <t>12045</t>
+  </si>
+  <si>
+    <t>12046</t>
+  </si>
+  <si>
+    <t>12050</t>
+  </si>
+  <si>
+    <t>12073</t>
+  </si>
+  <si>
+    <t>12074</t>
+  </si>
+  <si>
+    <t>12086</t>
+  </si>
+  <si>
+    <t>12094</t>
+  </si>
+  <si>
+    <t>12102</t>
+  </si>
+  <si>
+    <t>12110</t>
+  </si>
+  <si>
+    <t>12111</t>
+  </si>
+  <si>
+    <t>12120</t>
+  </si>
+  <si>
+    <t>12138</t>
+  </si>
+  <si>
+    <t>12139</t>
+  </si>
+  <si>
+    <t>12151</t>
+  </si>
+  <si>
+    <t>12169</t>
+  </si>
+  <si>
+    <t>12168</t>
+  </si>
+  <si>
+    <t>12170</t>
+  </si>
+  <si>
+    <t>12192</t>
+  </si>
+  <si>
+    <t>12207</t>
+  </si>
+  <si>
+    <t>12221</t>
+  </si>
+  <si>
+    <t>12231</t>
+  </si>
+  <si>
+    <t>12249</t>
+  </si>
+  <si>
+    <t>12250</t>
+  </si>
+  <si>
+    <t>12262</t>
+  </si>
+  <si>
+    <t>12276</t>
+  </si>
+  <si>
+    <t>12293</t>
+  </si>
+  <si>
+    <t>12309</t>
+  </si>
+  <si>
+    <t>12314</t>
+  </si>
+  <si>
+    <t>12325</t>
+  </si>
+  <si>
+    <t>12326</t>
+  </si>
+  <si>
+    <t>12327</t>
+  </si>
+  <si>
+    <t>12342</t>
+  </si>
+  <si>
+    <t>12343</t>
+  </si>
+  <si>
+    <t>12354</t>
+  </si>
+  <si>
+    <t>12355</t>
+  </si>
+  <si>
+    <t>12380</t>
+  </si>
+  <si>
+    <t>12382</t>
+  </si>
+  <si>
+    <t>12391</t>
+  </si>
+  <si>
+    <t>12392</t>
+  </si>
+  <si>
+    <t>12424</t>
+  </si>
+  <si>
+    <t>12425</t>
+  </si>
+  <si>
+    <t>12430</t>
+  </si>
+  <si>
+    <t>12434</t>
   </si>
 </sst>
 </file>
